--- a/data/source/weekly/cs-en-us-090pct.xlsx
+++ b/data/source/weekly/cs-en-us-090pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -878,8 +878,8 @@
       <c r="K14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L14" s="13" t="s">
-        <v>21</v>
+      <c r="L14" s="14">
+        <v>-100</v>
       </c>
       <c r="M14" s="14">
         <v>-100</v>
@@ -895,20 +895,20 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="15">
-        <v>1</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="15">
         <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I15" s="15">
         <v>1</v>
@@ -919,11 +919,11 @@
       <c r="K15" s="14">
         <v>-50</v>
       </c>
-      <c r="L15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="M15" s="13" t="s">
-        <v>21</v>
+      <c r="L15" s="14">
+        <v>0</v>
+      </c>
+      <c r="M15" s="14">
+        <v>0</v>
       </c>
       <c r="N15" s="14">
         <v>-85.714285714285</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" s="15">
         <v>4</v>
       </c>
       <c r="E16" s="14">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="F16" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G16" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H16" s="14">
-        <v>0</v>
+        <v>8.333333333333</v>
       </c>
       <c r="I16" s="15">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J16" s="15">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K16" s="14">
-        <v>14.285714285714</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L16" s="14">
-        <v>6.666666666666</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M16" s="14">
-        <v>-44.827586206896</v>
+        <v>-39.393939393939</v>
       </c>
       <c r="N16" s="14">
-        <v>-88.571428571428</v>
+        <v>-86.842105263157</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D17" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E17" s="14">
-        <v>-33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="F17" s="15">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G17" s="15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H17" s="14">
-        <v>76.923076923076</v>
+        <v>83.333333333333</v>
       </c>
       <c r="I17" s="15">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="J17" s="15">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K17" s="14">
-        <v>21.739130434782</v>
+        <v>38.461538461538</v>
       </c>
       <c r="L17" s="14">
-        <v>16.666666666666</v>
+        <v>16.129032258064</v>
       </c>
       <c r="M17" s="14">
-        <v>86.666666666666</v>
+        <v>80</v>
       </c>
       <c r="N17" s="14">
-        <v>-44</v>
+        <v>-43.75</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D18" s="15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E18" s="14">
-        <v>-71.428571428571</v>
+        <v>50</v>
       </c>
       <c r="F18" s="15">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G18" s="15">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H18" s="14">
-        <v>9.090909090909</v>
+        <v>36.842105263157</v>
       </c>
       <c r="I18" s="15">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="J18" s="15">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K18" s="14">
-        <v>42.307692307692</v>
+        <v>50</v>
       </c>
       <c r="L18" s="14">
-        <v>-30.188679245283</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="M18" s="14">
-        <v>-17.777777777777</v>
+        <v>-22.413793103448</v>
       </c>
       <c r="N18" s="14">
-        <v>-69.421487603305</v>
+        <v>-68.085106382978</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D19" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E19" s="14">
-        <v>54.545454545454</v>
+        <v>15.384615384615</v>
       </c>
       <c r="F19" s="15">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G19" s="15">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H19" s="14">
-        <v>4.255319148936</v>
+        <v>4.166666666666</v>
       </c>
       <c r="I19" s="15">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="J19" s="15">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="K19" s="14">
-        <v>20.338983050847</v>
+        <v>19.444444444444</v>
       </c>
       <c r="L19" s="14">
-        <v>10.9375</v>
+        <v>11.688311688311</v>
       </c>
       <c r="M19" s="14">
-        <v>65.116279069767</v>
+        <v>86.956521739130</v>
       </c>
       <c r="N19" s="14">
-        <v>57.777777777777</v>
+        <v>62.264150943396</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" s="14">
-        <v>100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G20" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H20" s="14">
-        <v>66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I20" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J20" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K20" s="14">
-        <v>18.181818181818</v>
+        <v>0</v>
       </c>
       <c r="L20" s="14">
-        <v>0</v>
+        <v>7.692307692307</v>
       </c>
       <c r="M20" s="14">
-        <v>-18.75</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="N20" s="14">
-        <v>-84.523809523809</v>
+        <v>-86.138613861386</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D21" s="17">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E21" s="18">
-        <v>-3.333333333333</v>
+        <v>14.814814814814</v>
       </c>
       <c r="F21" s="17">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G21" s="17">
         <v>100</v>
       </c>
       <c r="H21" s="18">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I21" s="17">
-        <v>166</v>
+        <v>202</v>
       </c>
       <c r="J21" s="17">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="K21" s="18">
-        <v>22.962962962963</v>
+        <v>24.691358024691</v>
       </c>
       <c r="L21" s="18">
-        <v>-1.775147928994</v>
+        <v>3.061224489795</v>
       </c>
       <c r="M21" s="18">
-        <v>11.409395973154</v>
+        <v>14.124293785310</v>
       </c>
       <c r="N21" s="18">
-        <v>-63.028953229398</v>
+        <v>-61.153846153846</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,20 +1182,20 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="15">
-        <v>2</v>
-      </c>
-      <c r="E22" s="14">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="15">
         <v>3</v>
       </c>
       <c r="G22" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H22" s="14">
-        <v>-40</v>
+        <v>-25</v>
       </c>
       <c r="I22" s="15">
         <v>6</v>
@@ -1209,8 +1209,8 @@
       <c r="L22" s="14">
         <v>100</v>
       </c>
-      <c r="M22" s="13" t="s">
-        <v>21</v>
+      <c r="M22" s="14">
+        <v>200</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23" s="15">
+        <v>6</v>
+      </c>
+      <c r="E23" s="14">
+        <v>-50</v>
+      </c>
+      <c r="F23" s="15">
+        <v>8</v>
+      </c>
+      <c r="G23" s="15">
+        <v>15</v>
+      </c>
+      <c r="H23" s="14">
+        <v>-46.666666666666</v>
+      </c>
+      <c r="I23" s="15">
+        <v>21</v>
+      </c>
+      <c r="J23" s="15">
+        <v>20</v>
+      </c>
+      <c r="K23" s="14">
         <v>5</v>
       </c>
-      <c r="E23" s="14">
-        <v>-80</v>
-      </c>
-      <c r="F23" s="15">
-        <v>10</v>
-      </c>
-      <c r="G23" s="15">
-        <v>10</v>
-      </c>
-      <c r="H23" s="14">
-        <v>0</v>
-      </c>
-      <c r="I23" s="15">
-        <v>16</v>
-      </c>
-      <c r="J23" s="15">
-        <v>14</v>
-      </c>
-      <c r="K23" s="14">
-        <v>14.285714285714</v>
-      </c>
       <c r="L23" s="14">
-        <v>14.285714285714</v>
+        <v>23.529411764705</v>
       </c>
       <c r="M23" s="14">
-        <v>33.333333333333</v>
+        <v>31.25</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D24" s="15">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E24" s="14">
-        <v>9.523809523809</v>
+        <v>-50</v>
       </c>
       <c r="F24" s="15">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="G24" s="15">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H24" s="14">
-        <v>21.951219512195</v>
+        <v>3.296703296703</v>
       </c>
       <c r="I24" s="15">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="J24" s="15">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="K24" s="14">
-        <v>37.5</v>
+        <v>20.714285714285</v>
       </c>
       <c r="L24" s="14">
-        <v>14.925373134328</v>
+        <v>12.666666666666</v>
       </c>
       <c r="M24" s="14">
-        <v>25.203252032520</v>
+        <v>21.582733812949</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D25" s="15">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E25" s="14">
-        <v>140</v>
+        <v>-90.909090909090</v>
       </c>
       <c r="F25" s="15">
+        <v>30</v>
+      </c>
+      <c r="G25" s="15">
         <v>35</v>
       </c>
-      <c r="G25" s="15">
-        <v>28</v>
-      </c>
       <c r="H25" s="14">
-        <v>25</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I25" s="15">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J25" s="15">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="K25" s="14">
-        <v>66.666666666666</v>
+        <v>29.787234042553</v>
       </c>
       <c r="L25" s="14">
-        <v>22.448979591836</v>
+        <v>10.909090909090</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D26" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E26" s="14">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F26" s="15">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G26" s="15">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H26" s="14">
-        <v>3.703703703703</v>
+        <v>37.5</v>
       </c>
       <c r="I26" s="15">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="J26" s="15">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K26" s="14">
-        <v>2.941176470588</v>
+        <v>26.315789473684</v>
       </c>
       <c r="L26" s="14">
-        <v>-39.655172413793</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="M26" s="14">
-        <v>-16.666666666666</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,20 +1387,20 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="15">
-        <v>1</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="15">
         <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I27" s="15">
         <v>1</v>
@@ -1411,8 +1411,8 @@
       <c r="K27" s="14">
         <v>-50</v>
       </c>
-      <c r="L27" s="13" t="s">
-        <v>21</v>
+      <c r="L27" s="14">
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,32 +1425,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>2</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G28" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H28" s="14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I28" s="15">
         <v>8</v>
       </c>
       <c r="J28" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K28" s="14">
-        <v>60</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L28" s="14">
         <v>14.285714285714</v>
@@ -1475,14 +1475,14 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="15">
-        <v>2</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="15">
         <v>1</v>
       </c>
       <c r="H29" s="14">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="I29" s="15">
         <v>2</v>
@@ -1500,7 +1500,7 @@
         <v>100</v>
       </c>
       <c r="N29" s="14">
-        <v>-83.333333333333</v>
+        <v>-86.666666666666</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1516,14 +1516,14 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="15">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="15">
         <v>1</v>
       </c>
       <c r="H30" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I30" s="15">
         <v>1</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="N30" s="14">
-        <v>-91.666666666666</v>
+        <v>-93.333333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="15">
-        <v>1</v>
-      </c>
-      <c r="E31" s="14">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="15">
         <v>2</v>
@@ -1576,7 +1576,7 @@
         <v>0</v>
       </c>
       <c r="L31" s="14">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-090pct.xlsx
+++ b/data/source/weekly/cs-en-us-090pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -937,37 +937,37 @@
         <v>3</v>
       </c>
       <c r="D16" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>-25</v>
+        <v>50</v>
       </c>
       <c r="F16" s="15">
+        <v>14</v>
+      </c>
+      <c r="G16" s="15">
         <v>13</v>
       </c>
-      <c r="G16" s="15">
-        <v>12</v>
-      </c>
       <c r="H16" s="14">
-        <v>8.333333333333</v>
+        <v>7.692307692307</v>
       </c>
       <c r="I16" s="15">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J16" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K16" s="14">
-        <v>11.111111111111</v>
+        <v>20</v>
       </c>
       <c r="L16" s="14">
-        <v>11.111111111111</v>
+        <v>4.347826086956</v>
       </c>
       <c r="M16" s="14">
-        <v>-39.393939393939</v>
+        <v>-31.428571428571</v>
       </c>
       <c r="N16" s="14">
-        <v>-86.842105263157</v>
+        <v>-86.127167630057</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>6</v>
       </c>
       <c r="D17" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E17" s="14">
+        <v>0</v>
+      </c>
+      <c r="F17" s="15">
+        <v>24</v>
+      </c>
+      <c r="G17" s="15">
+        <v>17</v>
+      </c>
+      <c r="H17" s="14">
+        <v>41.176470588235</v>
+      </c>
+      <c r="I17" s="15">
+        <v>42</v>
+      </c>
+      <c r="J17" s="15">
+        <v>32</v>
+      </c>
+      <c r="K17" s="14">
+        <v>31.25</v>
+      </c>
+      <c r="L17" s="14">
+        <v>10.526315789473</v>
+      </c>
+      <c r="M17" s="14">
         <v>100</v>
       </c>
-      <c r="F17" s="15">
-        <v>22</v>
-      </c>
-      <c r="G17" s="15">
-        <v>12</v>
-      </c>
-      <c r="H17" s="14">
-        <v>83.333333333333</v>
-      </c>
-      <c r="I17" s="15">
-        <v>36</v>
-      </c>
-      <c r="J17" s="15">
-        <v>26</v>
-      </c>
-      <c r="K17" s="14">
-        <v>38.461538461538</v>
-      </c>
-      <c r="L17" s="14">
-        <v>16.129032258064</v>
-      </c>
-      <c r="M17" s="14">
-        <v>80</v>
-      </c>
       <c r="N17" s="14">
-        <v>-43.75</v>
+        <v>-40.845070422535</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D18" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E18" s="14">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F18" s="15">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G18" s="15">
         <v>19</v>
       </c>
       <c r="H18" s="14">
-        <v>36.842105263157</v>
+        <v>63.157894736842</v>
       </c>
       <c r="I18" s="15">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="J18" s="15">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K18" s="14">
-        <v>50</v>
+        <v>57.142857142857</v>
       </c>
       <c r="L18" s="14">
-        <v>-18.181818181818</v>
+        <v>-11.290322580645</v>
       </c>
       <c r="M18" s="14">
-        <v>-22.413793103448</v>
+        <v>-14.0625</v>
       </c>
       <c r="N18" s="14">
-        <v>-68.085106382978</v>
+        <v>-65.838509316770</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D19" s="15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E19" s="14">
-        <v>15.384615384615</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F19" s="15">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G19" s="15">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="H19" s="14">
-        <v>4.166666666666</v>
+        <v>1.886792452830</v>
       </c>
       <c r="I19" s="15">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="J19" s="15">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="K19" s="14">
-        <v>19.444444444444</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L19" s="14">
-        <v>11.688311688311</v>
+        <v>2.083333333333</v>
       </c>
       <c r="M19" s="14">
-        <v>86.956521739130</v>
+        <v>71.929824561403</v>
       </c>
       <c r="N19" s="14">
-        <v>62.264150943396</v>
+        <v>66.101694915254</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>1</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" s="14">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G20" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H20" s="14">
-        <v>0</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I20" s="15">
         <v>14</v>
       </c>
       <c r="J20" s="15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K20" s="14">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="L20" s="14">
-        <v>7.692307692307</v>
+        <v>-12.5</v>
       </c>
       <c r="M20" s="14">
-        <v>-22.222222222222</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="N20" s="14">
-        <v>-86.138613861386</v>
+        <v>-88.429752066115</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D21" s="17">
         <v>27</v>
       </c>
       <c r="E21" s="18">
-        <v>14.814814814814</v>
+        <v>22.222222222222</v>
       </c>
       <c r="F21" s="17">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="G21" s="17">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="H21" s="18">
-        <v>19</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I21" s="17">
-        <v>202</v>
+        <v>234</v>
       </c>
       <c r="J21" s="17">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="K21" s="18">
-        <v>24.691358024691</v>
+        <v>23.809523809523</v>
       </c>
       <c r="L21" s="18">
-        <v>3.061224489795</v>
+        <v>-1.680672268907</v>
       </c>
       <c r="M21" s="18">
-        <v>14.124293785310</v>
+        <v>16.417910447761</v>
       </c>
       <c r="N21" s="18">
-        <v>-61.153846153846</v>
+        <v>-60.672268907563</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="C22" s="15">
+        <v>1</v>
+      </c>
+      <c r="D22" s="15">
+        <v>1</v>
+      </c>
+      <c r="E22" s="14">
+        <v>0</v>
       </c>
       <c r="F22" s="15">
         <v>3</v>
       </c>
       <c r="G22" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H22" s="14">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="I22" s="15">
+        <v>7</v>
+      </c>
+      <c r="J22" s="15">
         <v>6</v>
       </c>
-      <c r="J22" s="15">
-        <v>5</v>
-      </c>
       <c r="K22" s="14">
-        <v>20</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L22" s="14">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="M22" s="14">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D23" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E23" s="14">
-        <v>-50</v>
+        <v>25</v>
       </c>
       <c r="F23" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G23" s="15">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H23" s="14">
-        <v>-46.666666666666</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I23" s="15">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J23" s="15">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K23" s="14">
-        <v>5</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L23" s="14">
-        <v>23.529411764705</v>
+        <v>8.333333333333</v>
       </c>
       <c r="M23" s="14">
-        <v>31.25</v>
+        <v>52.941176470588</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D24" s="15">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E24" s="14">
-        <v>-50</v>
+        <v>69.230769230769</v>
       </c>
       <c r="F24" s="15">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="G24" s="15">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H24" s="14">
-        <v>3.296703296703</v>
+        <v>10.126582278481</v>
       </c>
       <c r="I24" s="15">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="J24" s="15">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="K24" s="14">
-        <v>20.714285714285</v>
+        <v>24.836601307189</v>
       </c>
       <c r="L24" s="14">
-        <v>12.666666666666</v>
+        <v>15.060240963855</v>
       </c>
       <c r="M24" s="14">
-        <v>21.582733812949</v>
+        <v>17.177914110429</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D25" s="15">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E25" s="14">
-        <v>-90.909090909090</v>
+        <v>20</v>
       </c>
       <c r="F25" s="15">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G25" s="15">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="H25" s="14">
-        <v>-14.285714285714</v>
+        <v>3.846153846153</v>
       </c>
       <c r="I25" s="15">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="J25" s="15">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="K25" s="14">
-        <v>29.787234042553</v>
+        <v>28.846153846153</v>
       </c>
       <c r="L25" s="14">
-        <v>10.909090909090</v>
+        <v>15.517241379310</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D26" s="15">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E26" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F26" s="15">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G26" s="15">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H26" s="14">
-        <v>37.5</v>
+        <v>18.518518518518</v>
       </c>
       <c r="I26" s="15">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="J26" s="15">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K26" s="14">
-        <v>26.315789473684</v>
+        <v>21.276595744680</v>
       </c>
       <c r="L26" s="14">
-        <v>-23.809523809523</v>
+        <v>-24</v>
       </c>
       <c r="M26" s="14">
-        <v>-5.882352941176</v>
+        <v>-3.389830508474</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="15">
+        <v>1</v>
       </c>
       <c r="D28" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" s="14">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F28" s="15">
         <v>5</v>
       </c>
       <c r="G28" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H28" s="14">
-        <v>25</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I28" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J28" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K28" s="14">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L28" s="14">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>100</v>
       </c>
       <c r="N29" s="14">
-        <v>-86.666666666666</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="N30" s="14">
-        <v>-93.333333333333</v>
+        <v>-93.75</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1558,10 +1558,10 @@
         <v>21</v>
       </c>
       <c r="F31" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" s="14">
         <v>0</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="15">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1625,8 +1625,8 @@
       <c r="H33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="13" t="s">
-        <v>20</v>
+      <c r="I33" s="15">
+        <v>1</v>
       </c>
       <c r="J33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-090pct.xlsx
+++ b/data/source/weekly/cs-en-us-090pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -901,32 +901,32 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="F15" s="15">
+        <v>1</v>
       </c>
       <c r="G15" s="15">
         <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="15">
         <v>2</v>
       </c>
       <c r="K15" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L15" s="14">
         <v>0</v>
       </c>
       <c r="M15" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N15" s="14">
-        <v>-85.714285714285</v>
+        <v>-71.428571428571</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="14">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="15">
         <v>14</v>
       </c>
       <c r="G16" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H16" s="14">
-        <v>7.692307692307</v>
+        <v>0</v>
       </c>
       <c r="I16" s="15">
+        <v>26</v>
+      </c>
+      <c r="J16" s="15">
         <v>24</v>
       </c>
-      <c r="J16" s="15">
-        <v>20</v>
-      </c>
       <c r="K16" s="14">
-        <v>20</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L16" s="14">
-        <v>4.347826086956</v>
+        <v>0</v>
       </c>
       <c r="M16" s="14">
-        <v>-31.428571428571</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="N16" s="14">
-        <v>-86.127167630057</v>
+        <v>-86.387434554973</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D17" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" s="14">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F17" s="15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G17" s="15">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H17" s="14">
-        <v>41.176470588235</v>
+        <v>13.636363636363</v>
       </c>
       <c r="I17" s="15">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="J17" s="15">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K17" s="14">
-        <v>31.25</v>
+        <v>28.205128205128</v>
       </c>
       <c r="L17" s="14">
-        <v>10.526315789473</v>
+        <v>21.951219512195</v>
       </c>
       <c r="M17" s="14">
-        <v>100</v>
+        <v>138.095238095238</v>
       </c>
       <c r="N17" s="14">
-        <v>-40.845070422535</v>
+        <v>-35.064935064935</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D18" s="15">
         <v>5</v>
       </c>
       <c r="E18" s="14">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F18" s="15">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G18" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H18" s="14">
-        <v>63.157894736842</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I18" s="15">
+        <v>62</v>
+      </c>
+      <c r="J18" s="15">
+        <v>40</v>
+      </c>
+      <c r="K18" s="14">
         <v>55</v>
       </c>
-      <c r="J18" s="15">
-        <v>35</v>
-      </c>
-      <c r="K18" s="14">
-        <v>57.142857142857</v>
-      </c>
       <c r="L18" s="14">
-        <v>-11.290322580645</v>
+        <v>-4.615384615384</v>
       </c>
       <c r="M18" s="14">
-        <v>-14.0625</v>
+        <v>-10.144927536231</v>
       </c>
       <c r="N18" s="14">
-        <v>-65.838509316770</v>
+        <v>-65.745856353591</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D19" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E19" s="14">
-        <v>16.666666666666</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="F19" s="15">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G19" s="15">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H19" s="14">
-        <v>1.886792452830</v>
+        <v>6.122448979591</v>
       </c>
       <c r="I19" s="15">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="J19" s="15">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="K19" s="14">
-        <v>16.666666666666</v>
+        <v>10.309278350515</v>
       </c>
       <c r="L19" s="14">
-        <v>2.083333333333</v>
+        <v>-8.547008547008</v>
       </c>
       <c r="M19" s="14">
-        <v>71.929824561403</v>
+        <v>67.1875</v>
       </c>
       <c r="N19" s="14">
-        <v>66.101694915254</v>
+        <v>62.121212121212</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="15">
+        <v>2</v>
       </c>
       <c r="D20" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="14">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F20" s="15">
         <v>5</v>
       </c>
       <c r="G20" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H20" s="14">
-        <v>-44.444444444444</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I20" s="15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J20" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K20" s="14">
-        <v>-12.5</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="L20" s="14">
-        <v>-12.5</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="M20" s="14">
-        <v>-36.363636363636</v>
+        <v>-36</v>
       </c>
       <c r="N20" s="14">
-        <v>-88.429752066115</v>
+        <v>-87.969924812030</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,63 +1139,63 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D21" s="17">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E21" s="18">
-        <v>22.222222222222</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="G21" s="17">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H21" s="18">
-        <v>14.285714285714</v>
+        <v>6.140350877192</v>
       </c>
       <c r="I21" s="17">
-        <v>234</v>
+        <v>263</v>
       </c>
       <c r="J21" s="17">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="K21" s="18">
-        <v>23.809523809523</v>
+        <v>20.091324200913</v>
       </c>
       <c r="L21" s="18">
-        <v>-1.680672268907</v>
+        <v>-3.308823529411</v>
       </c>
       <c r="M21" s="18">
-        <v>16.417910447761</v>
+        <v>20.091324200913</v>
       </c>
       <c r="N21" s="18">
-        <v>-60.672268907563</v>
+        <v>-60.030395136778</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="15">
         <v>1</v>
       </c>
-      <c r="D22" s="15">
-        <v>1</v>
-      </c>
-      <c r="E22" s="14">
-        <v>0</v>
-      </c>
-      <c r="F22" s="15">
+      <c r="G22" s="15">
         <v>3</v>
       </c>
-      <c r="G22" s="15">
-        <v>5</v>
-      </c>
       <c r="H22" s="14">
-        <v>-40</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I22" s="15">
         <v>7</v>
@@ -1207,7 +1207,7 @@
         <v>16.666666666666</v>
       </c>
       <c r="L22" s="14">
-        <v>133.333333333333</v>
+        <v>75</v>
       </c>
       <c r="M22" s="14">
         <v>75</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D23" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E23" s="14">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F23" s="15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G23" s="15">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H23" s="14">
-        <v>-44.444444444444</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="I23" s="15">
+        <v>29</v>
+      </c>
+      <c r="J23" s="15">
         <v>26</v>
       </c>
-      <c r="J23" s="15">
-        <v>24</v>
-      </c>
       <c r="K23" s="14">
-        <v>8.333333333333</v>
+        <v>11.538461538461</v>
       </c>
       <c r="L23" s="14">
-        <v>8.333333333333</v>
+        <v>3.571428571428</v>
       </c>
       <c r="M23" s="14">
-        <v>52.941176470588</v>
+        <v>52.631578947368</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D24" s="15">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E24" s="14">
-        <v>69.230769230769</v>
+        <v>0</v>
       </c>
       <c r="F24" s="15">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G24" s="15">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H24" s="14">
-        <v>10.126582278481</v>
+        <v>-2.564102564102</v>
       </c>
       <c r="I24" s="15">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="J24" s="15">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="K24" s="14">
-        <v>24.836601307189</v>
+        <v>21.893491124260</v>
       </c>
       <c r="L24" s="14">
-        <v>15.060240963855</v>
+        <v>6.185567010309</v>
       </c>
       <c r="M24" s="14">
-        <v>17.177914110429</v>
+        <v>16.384180790960</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D25" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E25" s="14">
-        <v>20</v>
+        <v>-25</v>
       </c>
       <c r="F25" s="15">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G25" s="15">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H25" s="14">
-        <v>3.846153846153</v>
+        <v>-12</v>
       </c>
       <c r="I25" s="15">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="J25" s="15">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K25" s="14">
-        <v>28.846153846153</v>
+        <v>25</v>
       </c>
       <c r="L25" s="14">
-        <v>15.517241379310</v>
+        <v>4.477611940298</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D26" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E26" s="14">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="F26" s="15">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G26" s="15">
         <v>27</v>
       </c>
       <c r="H26" s="14">
-        <v>18.518518518518</v>
+        <v>25.925925925925</v>
       </c>
       <c r="I26" s="15">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="J26" s="15">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="K26" s="14">
-        <v>21.276595744680</v>
+        <v>16.363636363636</v>
       </c>
       <c r="L26" s="14">
-        <v>-24</v>
+        <v>-28.089887640449</v>
       </c>
       <c r="M26" s="14">
-        <v>-3.389830508474</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1393,23 +1393,23 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+      <c r="F27" s="15">
+        <v>1</v>
       </c>
       <c r="G27" s="15">
         <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" s="15">
         <v>2</v>
       </c>
       <c r="K27" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L27" s="14">
         <v>0</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>1</v>
-      </c>
-      <c r="D28" s="15">
-        <v>3</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-66.666666666666</v>
+        <v>2</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
         <v>5</v>
       </c>
       <c r="G28" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H28" s="14">
-        <v>-28.571428571428</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I28" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J28" s="15">
         <v>9</v>
       </c>
       <c r="K28" s="14">
-        <v>0</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L28" s="14">
-        <v>0</v>
+        <v>22.222222222222</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1478,11 +1478,11 @@
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="15">
-        <v>1</v>
-      </c>
-      <c r="H29" s="14">
-        <v>-100</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="15">
         <v>2</v>
@@ -1500,7 +1500,7 @@
         <v>100</v>
       </c>
       <c r="N29" s="14">
-        <v>-87.5</v>
+        <v>-88.235294117647</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1519,11 +1519,11 @@
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="15">
-        <v>1</v>
-      </c>
-      <c r="H30" s="14">
-        <v>-100</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="15">
         <v>1</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="N30" s="14">
-        <v>-93.75</v>
+        <v>-94.117647058823</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="15">
+      <c r="D31" s="15">
         <v>1</v>
       </c>
+      <c r="E31" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
+      </c>
       <c r="G31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I31" s="15">
         <v>2</v>
       </c>
       <c r="J31" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L31" s="14">
         <v>-66.666666666666</v>
@@ -1634,8 +1634,8 @@
       <c r="K33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L33" s="13" t="s">
-        <v>21</v>
+      <c r="L33" s="14">
+        <v>-50</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-090pct.xlsx
+++ b/data/source/weekly/cs-en-us-090pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>1</v>
-      </c>
-      <c r="G15" s="15">
-        <v>1</v>
-      </c>
-      <c r="H15" s="14">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="15">
         <v>2</v>
       </c>
       <c r="K15" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L15" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M15" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N15" s="14">
-        <v>-71.428571428571</v>
+        <v>-57.142857142857</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>2</v>
       </c>
       <c r="D16" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="15">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G16" s="15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H16" s="14">
+        <v>-23.076923076923</v>
+      </c>
+      <c r="I16" s="15">
+        <v>27</v>
+      </c>
+      <c r="J16" s="15">
+        <v>27</v>
+      </c>
+      <c r="K16" s="14">
         <v>0</v>
       </c>
-      <c r="I16" s="15">
-        <v>26</v>
-      </c>
-      <c r="J16" s="15">
-        <v>24</v>
-      </c>
-      <c r="K16" s="14">
-        <v>8.333333333333</v>
-      </c>
       <c r="L16" s="14">
-        <v>0</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="M16" s="14">
-        <v>-31.578947368421</v>
+        <v>-38.636363636363</v>
       </c>
       <c r="N16" s="14">
-        <v>-86.387434554973</v>
+        <v>-87.383177570093</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D17" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E17" s="14">
-        <v>14.285714285714</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F17" s="15">
+        <v>26</v>
+      </c>
+      <c r="G17" s="15">
         <v>25</v>
       </c>
-      <c r="G17" s="15">
-        <v>22</v>
-      </c>
       <c r="H17" s="14">
-        <v>13.636363636363</v>
+        <v>4</v>
       </c>
       <c r="I17" s="15">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J17" s="15">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="K17" s="14">
-        <v>28.205128205128</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L17" s="14">
-        <v>21.951219512195</v>
+        <v>30.232558139534</v>
       </c>
       <c r="M17" s="14">
-        <v>138.095238095238</v>
+        <v>80.645161290322</v>
       </c>
       <c r="N17" s="14">
-        <v>-35.064935064935</v>
+        <v>-36.363636363636</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D18" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E18" s="14">
-        <v>20</v>
+        <v>62.5</v>
       </c>
       <c r="F18" s="15">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="G18" s="15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H18" s="14">
-        <v>14.285714285714</v>
+        <v>59.090909090909</v>
       </c>
       <c r="I18" s="15">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="J18" s="15">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="K18" s="14">
-        <v>55</v>
+        <v>58.333333333333</v>
       </c>
       <c r="L18" s="14">
-        <v>-4.615384615384</v>
+        <v>8.571428571428</v>
       </c>
       <c r="M18" s="14">
-        <v>-10.144927536231</v>
+        <v>5.555555555555</v>
       </c>
       <c r="N18" s="14">
-        <v>-65.745856353591</v>
+        <v>-65.765765765765</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="15">
         <v>13</v>
       </c>
       <c r="E19" s="14">
-        <v>-30.769230769230</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="F19" s="15">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G19" s="15">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H19" s="14">
-        <v>6.122448979591</v>
+        <v>-13.725490196078</v>
       </c>
       <c r="I19" s="15">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="J19" s="15">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="K19" s="14">
-        <v>10.309278350515</v>
+        <v>3.636363636363</v>
       </c>
       <c r="L19" s="14">
-        <v>-8.547008547008</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M19" s="14">
-        <v>67.1875</v>
+        <v>65.217391304347</v>
       </c>
       <c r="N19" s="14">
-        <v>62.121212121212</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D20" s="15">
         <v>1</v>
       </c>
       <c r="E20" s="14">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="F20" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G20" s="15">
         <v>7</v>
       </c>
       <c r="H20" s="14">
-        <v>-28.571428571428</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I20" s="15">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J20" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K20" s="14">
-        <v>-5.882352941176</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L20" s="14">
-        <v>-15.789473684210</v>
+        <v>5</v>
       </c>
       <c r="M20" s="14">
-        <v>-36</v>
+        <v>-34.375</v>
       </c>
       <c r="N20" s="14">
-        <v>-87.969924812030</v>
+        <v>-86.451612903225</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D21" s="17">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E21" s="18">
-        <v>-6.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G21" s="17">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H21" s="18">
-        <v>6.140350877192</v>
+        <v>5.932203389830</v>
       </c>
       <c r="I21" s="17">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="J21" s="17">
-        <v>219</v>
+        <v>253</v>
       </c>
       <c r="K21" s="18">
-        <v>20.091324200913</v>
+        <v>17.391304347826</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.308823529411</v>
+        <v>-0.668896321070</v>
       </c>
       <c r="M21" s="18">
-        <v>20.091324200913</v>
+        <v>18.8</v>
       </c>
       <c r="N21" s="18">
-        <v>-60.030395136778</v>
+        <v>-61.176470588235</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1192,10 +1192,10 @@
         <v>1</v>
       </c>
       <c r="G22" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H22" s="14">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I22" s="15">
         <v>7</v>
@@ -1210,7 +1210,7 @@
         <v>75</v>
       </c>
       <c r="M22" s="14">
-        <v>75</v>
+        <v>16.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
+        <v>4</v>
+      </c>
+      <c r="D23" s="15">
         <v>3</v>
       </c>
-      <c r="D23" s="15">
-        <v>2</v>
-      </c>
       <c r="E23" s="14">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F23" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G23" s="15">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H23" s="14">
-        <v>-23.529411764705</v>
+        <v>0</v>
       </c>
       <c r="I23" s="15">
+        <v>33</v>
+      </c>
+      <c r="J23" s="15">
         <v>29</v>
       </c>
-      <c r="J23" s="15">
-        <v>26</v>
-      </c>
       <c r="K23" s="14">
-        <v>11.538461538461</v>
+        <v>13.793103448275</v>
       </c>
       <c r="L23" s="14">
-        <v>3.571428571428</v>
+        <v>13.793103448275</v>
       </c>
       <c r="M23" s="14">
-        <v>52.631578947368</v>
+        <v>43.478260869565</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D24" s="15">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E24" s="14">
-        <v>0</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="F24" s="15">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G24" s="15">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H24" s="14">
-        <v>-2.564102564102</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="I24" s="15">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="J24" s="15">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="K24" s="14">
-        <v>21.893491124260</v>
+        <v>16.062176165803</v>
       </c>
       <c r="L24" s="14">
-        <v>6.185567010309</v>
+        <v>8.212560386473</v>
       </c>
       <c r="M24" s="14">
-        <v>16.384180790960</v>
+        <v>9.803921568627</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>3</v>
       </c>
       <c r="D25" s="15">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E25" s="14">
-        <v>-25</v>
+        <v>-62.5</v>
       </c>
       <c r="F25" s="15">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G25" s="15">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H25" s="14">
-        <v>-12</v>
+        <v>-50</v>
       </c>
       <c r="I25" s="15">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J25" s="15">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="K25" s="14">
-        <v>25</v>
+        <v>15.625</v>
       </c>
       <c r="L25" s="14">
-        <v>4.477611940298</v>
+        <v>7.246376811594</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D26" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E26" s="14">
-        <v>-12.5</v>
+        <v>83.333333333333</v>
       </c>
       <c r="F26" s="15">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G26" s="15">
         <v>27</v>
       </c>
       <c r="H26" s="14">
-        <v>25.925925925925</v>
+        <v>44.444444444444</v>
       </c>
       <c r="I26" s="15">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="J26" s="15">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="K26" s="14">
-        <v>16.363636363636</v>
+        <v>22.950819672131</v>
       </c>
       <c r="L26" s="14">
-        <v>-28.089887640449</v>
+        <v>-27.184466019417</v>
       </c>
       <c r="M26" s="14">
-        <v>-5.882352941176</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>1</v>
-      </c>
-      <c r="G27" s="15">
-        <v>1</v>
-      </c>
-      <c r="H27" s="14">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27" s="15">
         <v>2</v>
       </c>
       <c r="K27" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L27" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>2</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
       </c>
       <c r="F28" s="15">
+        <v>4</v>
+      </c>
+      <c r="G28" s="15">
         <v>5</v>
       </c>
-      <c r="G28" s="15">
-        <v>6</v>
-      </c>
       <c r="H28" s="14">
-        <v>-16.666666666666</v>
+        <v>-20</v>
       </c>
       <c r="I28" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J28" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K28" s="14">
-        <v>22.222222222222</v>
+        <v>20</v>
       </c>
       <c r="L28" s="14">
-        <v>22.222222222222</v>
+        <v>20</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1552,7 +1552,7 @@
         <v>20</v>
       </c>
       <c r="D31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" s="14">
         <v>-100</v>
@@ -1561,22 +1561,22 @@
         <v>20</v>
       </c>
       <c r="G31" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H31" s="14">
         <v>-100</v>
       </c>
       <c r="I31" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J31" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K31" s="14">
-        <v>-33.333333333333</v>
+        <v>-80</v>
       </c>
       <c r="L31" s="14">
-        <v>-66.666666666666</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-090pct.xlsx
+++ b/data/source/weekly/cs-en-us-090pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -329,8 +329,8 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#0"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0.00;&quot;-&quot;#,##0.00"/>
   </numFmts>
   <fonts count="12">
@@ -546,7 +546,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -564,7 +564,7 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -854,78 +854,78 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="L14" s="14">
+      <c r="J14" s="14">
+        <v>1</v>
+      </c>
+      <c r="K14" s="15">
         <v>-100</v>
       </c>
-      <c r="M14" s="14">
+      <c r="L14" s="15">
         <v>-100</v>
       </c>
-      <c r="N14" s="14">
+      <c r="M14" s="15">
+        <v>-100</v>
+      </c>
+      <c r="N14" s="15">
         <v>-100</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="15">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="15">
+        <v>22</v>
+      </c>
+      <c r="F15" s="14">
         <v>2</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I15" s="15">
+        <v>22</v>
+      </c>
+      <c r="I15" s="14">
         <v>3</v>
       </c>
-      <c r="J15" s="15">
+      <c r="J15" s="14">
         <v>2</v>
       </c>
-      <c r="K15" s="14">
+      <c r="K15" s="15">
         <v>50</v>
       </c>
-      <c r="L15" s="14">
+      <c r="L15" s="15">
         <v>50</v>
       </c>
-      <c r="M15" s="14">
+      <c r="M15" s="15">
         <v>200</v>
       </c>
-      <c r="N15" s="14">
+      <c r="N15" s="15">
         <v>-57.142857142857</v>
       </c>
     </row>
@@ -933,205 +933,205 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>2</v>
-      </c>
-      <c r="D16" s="15">
+      <c r="C16" s="14">
+        <v>6</v>
+      </c>
+      <c r="D16" s="14">
         <v>3</v>
       </c>
-      <c r="E16" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="F16" s="15">
+      <c r="E16" s="15">
+        <v>100</v>
+      </c>
+      <c r="F16" s="14">
+        <v>12</v>
+      </c>
+      <c r="G16" s="14">
+        <v>12</v>
+      </c>
+      <c r="H16" s="15">
+        <v>0</v>
+      </c>
+      <c r="I16" s="14">
+        <v>33</v>
+      </c>
+      <c r="J16" s="14">
+        <v>30</v>
+      </c>
+      <c r="K16" s="15">
         <v>10</v>
       </c>
-      <c r="G16" s="15">
-        <v>13</v>
-      </c>
-      <c r="H16" s="14">
-        <v>-23.076923076923</v>
-      </c>
-      <c r="I16" s="15">
-        <v>27</v>
-      </c>
-      <c r="J16" s="15">
-        <v>27</v>
-      </c>
-      <c r="K16" s="14">
-        <v>0</v>
-      </c>
-      <c r="L16" s="14">
-        <v>-6.896551724137</v>
-      </c>
-      <c r="M16" s="14">
-        <v>-38.636363636363</v>
-      </c>
-      <c r="N16" s="14">
-        <v>-87.383177570093</v>
+      <c r="L16" s="15">
+        <v>6.451612903225</v>
+      </c>
+      <c r="M16" s="15">
+        <v>-32.653061224489</v>
+      </c>
+      <c r="N16" s="15">
+        <v>-86.134453781512</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="14">
+        <v>3</v>
+      </c>
+      <c r="D17" s="14">
         <v>5</v>
       </c>
-      <c r="D17" s="15">
-        <v>9</v>
-      </c>
-      <c r="E17" s="14">
-        <v>-44.444444444444</v>
-      </c>
-      <c r="F17" s="15">
-        <v>26</v>
-      </c>
-      <c r="G17" s="15">
-        <v>25</v>
-      </c>
-      <c r="H17" s="14">
-        <v>4</v>
-      </c>
-      <c r="I17" s="15">
-        <v>56</v>
-      </c>
-      <c r="J17" s="15">
-        <v>48</v>
-      </c>
-      <c r="K17" s="14">
-        <v>16.666666666666</v>
-      </c>
-      <c r="L17" s="14">
-        <v>30.232558139534</v>
-      </c>
-      <c r="M17" s="14">
-        <v>80.645161290322</v>
-      </c>
-      <c r="N17" s="14">
-        <v>-36.363636363636</v>
+      <c r="E17" s="15">
+        <v>-40</v>
+      </c>
+      <c r="F17" s="14">
+        <v>23</v>
+      </c>
+      <c r="G17" s="14">
+        <v>27</v>
+      </c>
+      <c r="H17" s="15">
+        <v>-14.814814814814</v>
+      </c>
+      <c r="I17" s="14">
+        <v>58</v>
+      </c>
+      <c r="J17" s="14">
+        <v>53</v>
+      </c>
+      <c r="K17" s="15">
+        <v>9.433962264150</v>
+      </c>
+      <c r="L17" s="15">
+        <v>16</v>
+      </c>
+      <c r="M17" s="15">
+        <v>75.757575757575</v>
+      </c>
+      <c r="N17" s="15">
+        <v>-38.947368421052</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>13</v>
-      </c>
-      <c r="D18" s="15">
-        <v>8</v>
-      </c>
-      <c r="E18" s="14">
-        <v>62.5</v>
-      </c>
-      <c r="F18" s="15">
-        <v>35</v>
-      </c>
-      <c r="G18" s="15">
-        <v>22</v>
-      </c>
-      <c r="H18" s="14">
-        <v>59.090909090909</v>
-      </c>
-      <c r="I18" s="15">
-        <v>76</v>
-      </c>
-      <c r="J18" s="15">
-        <v>48</v>
-      </c>
-      <c r="K18" s="14">
-        <v>58.333333333333</v>
-      </c>
-      <c r="L18" s="14">
-        <v>8.571428571428</v>
-      </c>
-      <c r="M18" s="14">
-        <v>5.555555555555</v>
-      </c>
-      <c r="N18" s="14">
-        <v>-65.765765765765</v>
+      <c r="C18" s="14">
+        <v>4</v>
+      </c>
+      <c r="D18" s="14">
+        <v>3</v>
+      </c>
+      <c r="E18" s="15">
+        <v>33.333333333333</v>
+      </c>
+      <c r="F18" s="14">
+        <v>32</v>
+      </c>
+      <c r="G18" s="14">
+        <v>21</v>
+      </c>
+      <c r="H18" s="15">
+        <v>52.380952380952</v>
+      </c>
+      <c r="I18" s="14">
+        <v>79</v>
+      </c>
+      <c r="J18" s="14">
+        <v>51</v>
+      </c>
+      <c r="K18" s="15">
+        <v>54.901960784313</v>
+      </c>
+      <c r="L18" s="15">
+        <v>1.282051282051</v>
+      </c>
+      <c r="M18" s="15">
+        <v>1.282051282051</v>
+      </c>
+      <c r="N18" s="15">
+        <v>-68.016194331983</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="15">
-        <v>8</v>
-      </c>
-      <c r="D19" s="15">
-        <v>13</v>
-      </c>
-      <c r="E19" s="14">
-        <v>-38.461538461538</v>
-      </c>
-      <c r="F19" s="15">
-        <v>44</v>
-      </c>
-      <c r="G19" s="15">
-        <v>51</v>
-      </c>
-      <c r="H19" s="14">
-        <v>-13.725490196078</v>
-      </c>
-      <c r="I19" s="15">
-        <v>114</v>
-      </c>
-      <c r="J19" s="15">
-        <v>110</v>
-      </c>
-      <c r="K19" s="14">
-        <v>3.636363636363</v>
-      </c>
-      <c r="L19" s="14">
-        <v>-14.285714285714</v>
-      </c>
-      <c r="M19" s="14">
-        <v>65.217391304347</v>
-      </c>
-      <c r="N19" s="14">
-        <v>50</v>
+      <c r="C19" s="14">
+        <v>10</v>
+      </c>
+      <c r="D19" s="14">
+        <v>10</v>
+      </c>
+      <c r="E19" s="15">
+        <v>0</v>
+      </c>
+      <c r="F19" s="14">
+        <v>41</v>
+      </c>
+      <c r="G19" s="14">
+        <v>48</v>
+      </c>
+      <c r="H19" s="15">
+        <v>-14.583333333333</v>
+      </c>
+      <c r="I19" s="14">
+        <v>124</v>
+      </c>
+      <c r="J19" s="14">
+        <v>120</v>
+      </c>
+      <c r="K19" s="15">
+        <v>3.333333333333</v>
+      </c>
+      <c r="L19" s="15">
+        <v>-15.068493150684</v>
+      </c>
+      <c r="M19" s="15">
+        <v>67.567567567567</v>
+      </c>
+      <c r="N19" s="15">
+        <v>47.619047619047</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>5</v>
-      </c>
-      <c r="D20" s="15">
-        <v>1</v>
-      </c>
-      <c r="E20" s="14">
-        <v>400</v>
-      </c>
-      <c r="F20" s="15">
-        <v>8</v>
-      </c>
-      <c r="G20" s="15">
-        <v>7</v>
-      </c>
-      <c r="H20" s="14">
-        <v>14.285714285714</v>
-      </c>
-      <c r="I20" s="15">
-        <v>21</v>
-      </c>
-      <c r="J20" s="15">
-        <v>18</v>
-      </c>
-      <c r="K20" s="14">
-        <v>16.666666666666</v>
-      </c>
-      <c r="L20" s="14">
-        <v>5</v>
-      </c>
-      <c r="M20" s="14">
-        <v>-34.375</v>
-      </c>
-      <c r="N20" s="14">
-        <v>-86.451612903225</v>
+      <c r="C20" s="14">
+        <v>2</v>
+      </c>
+      <c r="D20" s="14">
+        <v>2</v>
+      </c>
+      <c r="E20" s="15">
+        <v>0</v>
+      </c>
+      <c r="F20" s="14">
+        <v>9</v>
+      </c>
+      <c r="G20" s="14">
+        <v>6</v>
+      </c>
+      <c r="H20" s="15">
+        <v>50</v>
+      </c>
+      <c r="I20" s="14">
+        <v>23</v>
+      </c>
+      <c r="J20" s="14">
+        <v>20</v>
+      </c>
+      <c r="K20" s="15">
+        <v>15</v>
+      </c>
+      <c r="L20" s="15">
+        <v>0</v>
+      </c>
+      <c r="M20" s="15">
+        <v>-30.303030303030</v>
+      </c>
+      <c r="N20" s="15">
+        <v>-85.889570552147</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,327 +1139,327 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D21" s="17">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>4.166666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="G21" s="17">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H21" s="18">
-        <v>5.932203389830</v>
+        <v>3.478260869565</v>
       </c>
       <c r="I21" s="17">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="J21" s="17">
-        <v>253</v>
+        <v>277</v>
       </c>
       <c r="K21" s="18">
-        <v>17.391304347826</v>
+        <v>15.523465703971</v>
       </c>
       <c r="L21" s="18">
-        <v>-0.668896321070</v>
+        <v>-3.614457831325</v>
       </c>
       <c r="M21" s="18">
-        <v>18.8</v>
+        <v>18.959107806691</v>
       </c>
       <c r="N21" s="18">
-        <v>-61.176470588235</v>
+        <v>-61.813842482100</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="15">
+        <v>22</v>
+      </c>
+      <c r="F22" s="14">
+        <v>2</v>
+      </c>
+      <c r="G22" s="14">
         <v>1</v>
       </c>
-      <c r="G22" s="15">
-        <v>1</v>
-      </c>
-      <c r="H22" s="14">
-        <v>0</v>
-      </c>
-      <c r="I22" s="15">
-        <v>7</v>
-      </c>
-      <c r="J22" s="15">
+      <c r="H22" s="15">
+        <v>100</v>
+      </c>
+      <c r="I22" s="14">
+        <v>8</v>
+      </c>
+      <c r="J22" s="14">
         <v>6</v>
       </c>
-      <c r="K22" s="14">
-        <v>16.666666666666</v>
-      </c>
-      <c r="L22" s="14">
-        <v>75</v>
-      </c>
-      <c r="M22" s="14">
-        <v>16.666666666666</v>
+      <c r="K22" s="15">
+        <v>33.333333333333</v>
+      </c>
+      <c r="L22" s="15">
+        <v>100</v>
+      </c>
+      <c r="M22" s="15">
+        <v>33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>4</v>
-      </c>
-      <c r="D23" s="15">
+      <c r="C23" s="14">
+        <v>5</v>
+      </c>
+      <c r="D23" s="14">
         <v>3</v>
       </c>
-      <c r="E23" s="14">
-        <v>33.333333333333</v>
-      </c>
-      <c r="F23" s="15">
-        <v>15</v>
-      </c>
-      <c r="G23" s="15">
-        <v>15</v>
-      </c>
-      <c r="H23" s="14">
-        <v>0</v>
-      </c>
-      <c r="I23" s="15">
-        <v>33</v>
-      </c>
-      <c r="J23" s="15">
-        <v>29</v>
-      </c>
-      <c r="K23" s="14">
-        <v>13.793103448275</v>
-      </c>
-      <c r="L23" s="14">
-        <v>13.793103448275</v>
-      </c>
-      <c r="M23" s="14">
-        <v>43.478260869565</v>
+      <c r="E23" s="15">
+        <v>66.666666666666</v>
+      </c>
+      <c r="F23" s="14">
+        <v>17</v>
+      </c>
+      <c r="G23" s="14">
+        <v>12</v>
+      </c>
+      <c r="H23" s="15">
+        <v>41.666666666666</v>
+      </c>
+      <c r="I23" s="14">
+        <v>38</v>
+      </c>
+      <c r="J23" s="14">
+        <v>32</v>
+      </c>
+      <c r="K23" s="15">
+        <v>18.75</v>
+      </c>
+      <c r="L23" s="15">
+        <v>15.151515151515</v>
+      </c>
+      <c r="M23" s="15">
+        <v>46.153846153846</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="15">
-        <v>17</v>
-      </c>
-      <c r="D24" s="15">
-        <v>24</v>
-      </c>
-      <c r="E24" s="14">
-        <v>-29.166666666666</v>
-      </c>
-      <c r="F24" s="15">
-        <v>69</v>
-      </c>
-      <c r="G24" s="15">
-        <v>81</v>
-      </c>
-      <c r="H24" s="14">
-        <v>-14.814814814814</v>
-      </c>
-      <c r="I24" s="15">
-        <v>224</v>
-      </c>
-      <c r="J24" s="15">
-        <v>193</v>
-      </c>
-      <c r="K24" s="14">
-        <v>16.062176165803</v>
-      </c>
-      <c r="L24" s="14">
-        <v>8.212560386473</v>
-      </c>
-      <c r="M24" s="14">
-        <v>9.803921568627</v>
+      <c r="C24" s="14">
+        <v>30</v>
+      </c>
+      <c r="D24" s="14">
+        <v>23</v>
+      </c>
+      <c r="E24" s="15">
+        <v>30.434782608695</v>
+      </c>
+      <c r="F24" s="14">
+        <v>85</v>
+      </c>
+      <c r="G24" s="14">
+        <v>76</v>
+      </c>
+      <c r="H24" s="15">
+        <v>11.842105263157</v>
+      </c>
+      <c r="I24" s="14">
+        <v>253</v>
+      </c>
+      <c r="J24" s="14">
+        <v>216</v>
+      </c>
+      <c r="K24" s="15">
+        <v>17.129629629629</v>
+      </c>
+      <c r="L24" s="15">
+        <v>14.479638009049</v>
+      </c>
+      <c r="M24" s="15">
+        <v>13.963963963964</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="15">
+      <c r="C25" s="14">
         <v>3</v>
       </c>
-      <c r="D25" s="15">
-        <v>8</v>
-      </c>
-      <c r="E25" s="14">
-        <v>-62.5</v>
-      </c>
-      <c r="F25" s="15">
-        <v>14</v>
-      </c>
-      <c r="G25" s="15">
-        <v>28</v>
-      </c>
-      <c r="H25" s="14">
-        <v>-50</v>
-      </c>
-      <c r="I25" s="15">
-        <v>74</v>
-      </c>
-      <c r="J25" s="15">
-        <v>64</v>
-      </c>
-      <c r="K25" s="14">
-        <v>15.625</v>
-      </c>
-      <c r="L25" s="14">
-        <v>7.246376811594</v>
+      <c r="D25" s="14">
+        <v>3</v>
+      </c>
+      <c r="E25" s="15">
+        <v>0</v>
+      </c>
+      <c r="F25" s="14">
+        <v>16</v>
+      </c>
+      <c r="G25" s="14">
+        <v>20</v>
+      </c>
+      <c r="H25" s="15">
+        <v>-20</v>
+      </c>
+      <c r="I25" s="14">
+        <v>77</v>
+      </c>
+      <c r="J25" s="14">
+        <v>67</v>
+      </c>
+      <c r="K25" s="15">
+        <v>14.925373134328</v>
+      </c>
+      <c r="L25" s="15">
+        <v>2.666666666666</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="15">
-        <v>11</v>
-      </c>
-      <c r="D26" s="15">
+      <c r="C26" s="14">
+        <v>7</v>
+      </c>
+      <c r="D26" s="14">
         <v>6</v>
       </c>
-      <c r="E26" s="14">
-        <v>83.333333333333</v>
-      </c>
-      <c r="F26" s="15">
-        <v>39</v>
-      </c>
-      <c r="G26" s="15">
-        <v>27</v>
-      </c>
-      <c r="H26" s="14">
-        <v>44.444444444444</v>
-      </c>
-      <c r="I26" s="15">
-        <v>75</v>
-      </c>
-      <c r="J26" s="15">
-        <v>61</v>
-      </c>
-      <c r="K26" s="14">
-        <v>22.950819672131</v>
-      </c>
-      <c r="L26" s="14">
-        <v>-27.184466019417</v>
-      </c>
-      <c r="M26" s="14">
-        <v>-3.846153846153</v>
+      <c r="E26" s="15">
+        <v>16.666666666666</v>
+      </c>
+      <c r="F26" s="14">
+        <v>34</v>
+      </c>
+      <c r="G26" s="14">
+        <v>29</v>
+      </c>
+      <c r="H26" s="15">
+        <v>17.241379310344</v>
+      </c>
+      <c r="I26" s="14">
+        <v>83</v>
+      </c>
+      <c r="J26" s="14">
+        <v>67</v>
+      </c>
+      <c r="K26" s="15">
+        <v>23.880597014925</v>
+      </c>
+      <c r="L26" s="15">
+        <v>-30.833333333333</v>
+      </c>
+      <c r="M26" s="15">
+        <v>-6.741573033707</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="15">
+        <v>22</v>
+      </c>
+      <c r="F27" s="14">
         <v>2</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I27" s="15">
+        <v>22</v>
+      </c>
+      <c r="I27" s="14">
         <v>3</v>
       </c>
-      <c r="J27" s="15">
+      <c r="J27" s="14">
         <v>2</v>
       </c>
-      <c r="K27" s="14">
+      <c r="K27" s="15">
         <v>50</v>
       </c>
-      <c r="L27" s="14">
+      <c r="L27" s="15">
         <v>50</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
-      </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F28" s="14">
+        <v>4</v>
+      </c>
+      <c r="G28" s="14">
+        <v>6</v>
+      </c>
+      <c r="H28" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="I28" s="14">
+        <v>12</v>
+      </c>
+      <c r="J28" s="14">
+        <v>12</v>
+      </c>
+      <c r="K28" s="15">
         <v>0</v>
       </c>
-      <c r="F28" s="15">
-        <v>4</v>
-      </c>
-      <c r="G28" s="15">
-        <v>5</v>
-      </c>
-      <c r="H28" s="14">
-        <v>-20</v>
-      </c>
-      <c r="I28" s="15">
-        <v>12</v>
-      </c>
-      <c r="J28" s="15">
-        <v>10</v>
-      </c>
-      <c r="K28" s="14">
-        <v>20</v>
-      </c>
-      <c r="L28" s="14">
+      <c r="L28" s="15">
         <v>20</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1469,38 +1469,38 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I29" s="15">
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>-100</v>
+      </c>
+      <c r="I29" s="14">
         <v>2</v>
       </c>
-      <c r="J29" s="15">
-        <v>1</v>
-      </c>
-      <c r="K29" s="14">
+      <c r="J29" s="14">
+        <v>2</v>
+      </c>
+      <c r="K29" s="15">
+        <v>0</v>
+      </c>
+      <c r="L29" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M29" s="15">
         <v>100</v>
       </c>
-      <c r="L29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="M29" s="14">
-        <v>100</v>
-      </c>
-      <c r="N29" s="14">
-        <v>-88.235294117647</v>
+      <c r="N29" s="15">
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,79 +1510,79 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I30" s="15">
+      <c r="G30" s="14">
         <v>1</v>
       </c>
-      <c r="J30" s="15">
+      <c r="H30" s="15">
+        <v>-100</v>
+      </c>
+      <c r="I30" s="14">
         <v>1</v>
       </c>
-      <c r="K30" s="14">
+      <c r="J30" s="14">
+        <v>2</v>
+      </c>
+      <c r="K30" s="15">
+        <v>-50</v>
+      </c>
+      <c r="L30" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M30" s="15">
         <v>0</v>
       </c>
-      <c r="L30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="M30" s="14">
-        <v>0</v>
-      </c>
-      <c r="N30" s="14">
-        <v>-94.117647058823</v>
+      <c r="N30" s="15">
+        <v>-94.444444444444</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="15">
+      <c r="C31" s="14">
+        <v>1</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F31" s="14">
+        <v>1</v>
+      </c>
+      <c r="G31" s="14">
+        <v>3</v>
+      </c>
+      <c r="H31" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="I31" s="14">
         <v>2</v>
       </c>
-      <c r="E31" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G31" s="15">
-        <v>3</v>
-      </c>
-      <c r="H31" s="14">
-        <v>-100</v>
-      </c>
-      <c r="I31" s="15">
-        <v>1</v>
-      </c>
-      <c r="J31" s="15">
+      <c r="J31" s="14">
         <v>5</v>
       </c>
-      <c r="K31" s="14">
-        <v>-80</v>
-      </c>
-      <c r="L31" s="14">
-        <v>-83.333333333333</v>
+      <c r="K31" s="15">
+        <v>-60</v>
+      </c>
+      <c r="L31" s="15">
+        <v>-66.666666666666</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,34 +1614,34 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F33" s="15">
+        <v>22</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I33" s="14">
         <v>1</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I33" s="15">
-        <v>1</v>
-      </c>
       <c r="J33" s="13" t="s">
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="L33" s="14">
+        <v>22</v>
+      </c>
+      <c r="L33" s="15">
         <v>-50</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1742,63 +1742,63 @@
       <c r="A39" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="14">
         <v>24</v>
       </c>
-      <c r="E39" s="15">
-        <v>22</v>
-      </c>
-      <c r="G39" s="15">
+      <c r="E39" s="14">
+        <v>22</v>
+      </c>
+      <c r="G39" s="14">
         <v>2</v>
       </c>
-      <c r="I39" s="15">
+      <c r="I39" s="14">
         <v>12</v>
       </c>
-      <c r="J39" s="15">
+      <c r="J39" s="14">
         <v>3</v>
       </c>
-      <c r="K39" s="14">
+      <c r="K39" s="15">
         <v>-75</v>
       </c>
-      <c r="L39" s="14">
+      <c r="L39" s="15">
         <v>50</v>
       </c>
-      <c r="M39" s="14">
+      <c r="M39" s="15">
         <v>-86.363636363636</v>
       </c>
-      <c r="N39" s="14">
+      <c r="N39" s="15">
         <v>-87.5</v>
       </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C40" s="15">
+        <v>21</v>
+      </c>
+      <c r="C40" s="14">
         <v>43</v>
       </c>
-      <c r="E40" s="15">
+      <c r="E40" s="14">
         <v>34</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="14">
         <v>29</v>
       </c>
-      <c r="I40" s="15">
+      <c r="I40" s="14">
         <v>24</v>
       </c>
-      <c r="J40" s="15">
+      <c r="J40" s="14">
         <v>23</v>
       </c>
-      <c r="K40" s="14">
+      <c r="K40" s="15">
         <v>-4.166666666666</v>
       </c>
-      <c r="L40" s="14">
+      <c r="L40" s="15">
         <v>-20.689655172413</v>
       </c>
-      <c r="M40" s="14">
+      <c r="M40" s="15">
         <v>-32.352941176470</v>
       </c>
-      <c r="N40" s="14">
+      <c r="N40" s="15">
         <v>-46.511627906976</v>
       </c>
     </row>
@@ -1806,31 +1806,31 @@
       <c r="A41" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="14">
         <v>1604</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="14">
         <v>1297</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="14">
         <v>585</v>
       </c>
-      <c r="I41" s="15">
+      <c r="I41" s="14">
         <v>507</v>
       </c>
-      <c r="J41" s="15">
+      <c r="J41" s="14">
         <v>203</v>
       </c>
-      <c r="K41" s="14">
+      <c r="K41" s="15">
         <v>-59.960552268244</v>
       </c>
-      <c r="L41" s="14">
+      <c r="L41" s="15">
         <v>-65.299145299145</v>
       </c>
-      <c r="M41" s="14">
+      <c r="M41" s="15">
         <v>-84.348496530454</v>
       </c>
-      <c r="N41" s="14">
+      <c r="N41" s="15">
         <v>-87.344139650872</v>
       </c>
     </row>
@@ -1838,31 +1838,31 @@
       <c r="A42" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="14">
         <v>619</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="14">
         <v>579</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="14">
         <v>314</v>
       </c>
-      <c r="I42" s="15">
+      <c r="I42" s="14">
         <v>279</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="14">
         <v>295</v>
       </c>
-      <c r="K42" s="14">
+      <c r="K42" s="15">
         <v>5.734767025089</v>
       </c>
-      <c r="L42" s="14">
+      <c r="L42" s="15">
         <v>-6.050955414012</v>
       </c>
-      <c r="M42" s="14">
+      <c r="M42" s="15">
         <v>-49.050086355785</v>
       </c>
-      <c r="N42" s="14">
+      <c r="N42" s="15">
         <v>-52.342487883683</v>
       </c>
     </row>
@@ -1870,31 +1870,31 @@
       <c r="A43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="14">
         <v>1345</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="14">
         <v>1322</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="14">
         <v>490</v>
       </c>
-      <c r="I43" s="15">
+      <c r="I43" s="14">
         <v>484</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="14">
         <v>252</v>
       </c>
-      <c r="K43" s="14">
+      <c r="K43" s="15">
         <v>-47.933884297520</v>
       </c>
-      <c r="L43" s="14">
+      <c r="L43" s="15">
         <v>-48.571428571428</v>
       </c>
-      <c r="M43" s="14">
+      <c r="M43" s="15">
         <v>-80.937972768532</v>
       </c>
-      <c r="N43" s="14">
+      <c r="N43" s="15">
         <v>-81.263940520446</v>
       </c>
     </row>
@@ -1902,31 +1902,31 @@
       <c r="A44" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="14">
         <v>588</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="14">
         <v>556</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="14">
         <v>300</v>
       </c>
-      <c r="I44" s="15">
+      <c r="I44" s="14">
         <v>372</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="14">
         <v>788</v>
       </c>
-      <c r="K44" s="14">
+      <c r="K44" s="15">
         <v>111.827956989247</v>
       </c>
-      <c r="L44" s="14">
+      <c r="L44" s="15">
         <v>162.666666666667</v>
       </c>
-      <c r="M44" s="14">
+      <c r="M44" s="15">
         <v>41.726618705036</v>
       </c>
-      <c r="N44" s="14">
+      <c r="N44" s="15">
         <v>34.013605442176</v>
       </c>
     </row>
@@ -1934,31 +1934,31 @@
       <c r="A45" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="14">
         <v>1169</v>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="14">
         <v>941</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="14">
         <v>465</v>
       </c>
-      <c r="I45" s="15">
+      <c r="I45" s="14">
         <v>336</v>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="14">
         <v>122</v>
       </c>
-      <c r="K45" s="14">
+      <c r="K45" s="15">
         <v>-63.690476190476</v>
       </c>
-      <c r="L45" s="14">
+      <c r="L45" s="15">
         <v>-73.763440860215</v>
       </c>
-      <c r="M45" s="14">
+      <c r="M45" s="15">
         <v>-87.035069075451</v>
       </c>
-      <c r="N45" s="14">
+      <c r="N45" s="15">
         <v>-89.563729683490</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-090pct.xlsx
+++ b/data/source/weekly/cs-en-us-090pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -205,28 +205,28 @@
     <t>Rape</t>
   </si>
   <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
   </si>
   <si>
     <t>Housing</t>
@@ -864,7 +864,7 @@
         <v>20</v>
       </c>
       <c r="G14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="15">
         <v>-100</v>
@@ -873,7 +873,7 @@
         <v>20</v>
       </c>
       <c r="J14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" s="15">
         <v>-100</v>
@@ -892,369 +892,369 @@
       <c r="A15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>22</v>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>22</v>
+        <v>3</v>
+      </c>
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15">
+        <v>200</v>
       </c>
       <c r="I15" s="14">
+        <v>4</v>
+      </c>
+      <c r="J15" s="14">
         <v>3</v>
       </c>
-      <c r="J15" s="14">
-        <v>2</v>
-      </c>
       <c r="K15" s="15">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M15" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="N15" s="15">
-        <v>-57.142857142857</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="14">
+        <v>2</v>
+      </c>
+      <c r="D16" s="14">
         <v>6</v>
       </c>
-      <c r="D16" s="14">
-        <v>3</v>
-      </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>-31.25</v>
       </c>
       <c r="I16" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J16" s="14">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="K16" s="15">
-        <v>10</v>
+        <v>-2.777777777777</v>
       </c>
       <c r="L16" s="15">
-        <v>6.451612903225</v>
+        <v>6.060606060606</v>
       </c>
       <c r="M16" s="15">
-        <v>-32.653061224489</v>
+        <v>-39.655172413793</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.134453781512</v>
+        <v>-86.274509803921</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="14">
+        <v>2</v>
+      </c>
+      <c r="D17" s="14">
+        <v>3</v>
+      </c>
+      <c r="E17" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="F17" s="14">
+        <v>19</v>
+      </c>
+      <c r="G17" s="14">
         <v>24</v>
       </c>
-      <c r="C17" s="14">
-        <v>3</v>
-      </c>
-      <c r="D17" s="14">
-        <v>5</v>
-      </c>
-      <c r="E17" s="15">
-        <v>-40</v>
-      </c>
-      <c r="F17" s="14">
-        <v>23</v>
-      </c>
-      <c r="G17" s="14">
-        <v>27</v>
-      </c>
       <c r="H17" s="15">
-        <v>-14.814814814814</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J17" s="14">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K17" s="15">
-        <v>9.433962264150</v>
+        <v>7.142857142857</v>
       </c>
       <c r="L17" s="15">
-        <v>16</v>
+        <v>7.142857142857</v>
       </c>
       <c r="M17" s="15">
-        <v>75.757575757575</v>
+        <v>76.470588235294</v>
       </c>
       <c r="N17" s="15">
-        <v>-38.947368421052</v>
+        <v>-43.925233644859</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="14">
         <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G18" s="14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H18" s="15">
-        <v>52.380952380952</v>
+        <v>44.444444444444</v>
       </c>
       <c r="I18" s="14">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J18" s="14">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K18" s="15">
-        <v>54.901960784313</v>
+        <v>56.603773584905</v>
       </c>
       <c r="L18" s="15">
-        <v>1.282051282051</v>
+        <v>0</v>
       </c>
       <c r="M18" s="15">
-        <v>1.282051282051</v>
+        <v>3.75</v>
       </c>
       <c r="N18" s="15">
-        <v>-68.016194331983</v>
+        <v>-69.708029197080</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>7.142857142857</v>
       </c>
       <c r="F19" s="14">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G19" s="14">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H19" s="15">
-        <v>-14.583333333333</v>
+        <v>-12</v>
       </c>
       <c r="I19" s="14">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="J19" s="14">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="K19" s="15">
-        <v>3.333333333333</v>
+        <v>5.223880597014</v>
       </c>
       <c r="L19" s="15">
-        <v>-15.068493150684</v>
+        <v>-16.071428571428</v>
       </c>
       <c r="M19" s="15">
-        <v>67.567567567567</v>
+        <v>65.882352941176</v>
       </c>
       <c r="N19" s="15">
-        <v>47.619047619047</v>
+        <v>56.666666666666</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F20" s="14">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G20" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H20" s="15">
-        <v>50</v>
+        <v>220</v>
       </c>
       <c r="I20" s="14">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J20" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K20" s="15">
-        <v>15</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L20" s="15">
-        <v>0</v>
+        <v>30.434782608695</v>
       </c>
       <c r="M20" s="15">
-        <v>-30.303030303030</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.889570552147</v>
+        <v>-83.240223463687</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="17">
+        <v>31</v>
+      </c>
+      <c r="D21" s="17">
         <v>28</v>
       </c>
-      <c r="C21" s="17">
-        <v>25</v>
-      </c>
-      <c r="D21" s="17">
-        <v>24</v>
-      </c>
       <c r="E21" s="18">
-        <v>4.166666666666</v>
+        <v>10.714285714285</v>
       </c>
       <c r="F21" s="17">
         <v>119</v>
       </c>
       <c r="G21" s="17">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H21" s="18">
-        <v>3.478260869565</v>
+        <v>2.586206896551</v>
       </c>
       <c r="I21" s="17">
-        <v>320</v>
+        <v>353</v>
       </c>
       <c r="J21" s="17">
-        <v>277</v>
+        <v>305</v>
       </c>
       <c r="K21" s="18">
-        <v>15.523465703971</v>
+        <v>15.737704918032</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.614457831325</v>
+        <v>-3.814713896457</v>
       </c>
       <c r="M21" s="18">
-        <v>18.959107806691</v>
+        <v>20.068027210884</v>
       </c>
       <c r="N21" s="18">
-        <v>-61.813842482100</v>
+        <v>-61.504907306434</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="14">
+        <v>28</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>22</v>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="14">
         <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
         <v>8</v>
       </c>
       <c r="J22" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K22" s="15">
+        <v>14.285714285714</v>
+      </c>
+      <c r="L22" s="15">
         <v>33.333333333333</v>
       </c>
-      <c r="L22" s="15">
-        <v>100</v>
-      </c>
       <c r="M22" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>5</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G23" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H23" s="15">
-        <v>41.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I23" s="14">
         <v>38</v>
       </c>
       <c r="J23" s="14">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K23" s="15">
-        <v>18.75</v>
+        <v>15.151515151515</v>
       </c>
       <c r="L23" s="15">
-        <v>15.151515151515</v>
+        <v>-2.564102564102</v>
       </c>
       <c r="M23" s="15">
         <v>46.153846153846</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D24" s="14">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15">
-        <v>30.434782608695</v>
+        <v>0</v>
       </c>
       <c r="F24" s="14">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G24" s="14">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H24" s="15">
-        <v>11.842105263157</v>
+        <v>-1.219512195121</v>
       </c>
       <c r="I24" s="14">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="J24" s="14">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="K24" s="15">
-        <v>17.129629629629</v>
+        <v>14.893617021276</v>
       </c>
       <c r="L24" s="15">
-        <v>14.479638009049</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M24" s="15">
-        <v>13.963963963964</v>
+        <v>9.756097560975</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F25" s="14">
         <v>16</v>
       </c>
       <c r="G25" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H25" s="15">
-        <v>-20</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I25" s="14">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="J25" s="14">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="K25" s="15">
-        <v>14.925373134328</v>
+        <v>12.162162162162</v>
       </c>
       <c r="L25" s="15">
-        <v>2.666666666666</v>
+        <v>-3.488372093023</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1347,119 +1347,119 @@
         <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E26" s="15">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G26" s="14">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H26" s="15">
-        <v>17.241379310344</v>
+        <v>18.518518518518</v>
       </c>
       <c r="I26" s="14">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="J26" s="14">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="K26" s="15">
-        <v>23.880597014925</v>
+        <v>21.621621621621</v>
       </c>
       <c r="L26" s="15">
-        <v>-30.833333333333</v>
+        <v>-27.419354838709</v>
       </c>
       <c r="M26" s="15">
-        <v>-6.741573033707</v>
+        <v>-4.255319148936</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>22</v>
+      <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>22</v>
+        <v>3</v>
+      </c>
+      <c r="G27" s="14">
+        <v>1</v>
+      </c>
+      <c r="H27" s="15">
+        <v>200</v>
       </c>
       <c r="I27" s="14">
+        <v>4</v>
+      </c>
+      <c r="J27" s="14">
         <v>3</v>
       </c>
-      <c r="J27" s="14">
-        <v>2</v>
-      </c>
       <c r="K27" s="15">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="14">
+        <v>3</v>
+      </c>
+      <c r="D28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="E28" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>-33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="I28" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J28" s="14">
         <v>12</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L28" s="15">
-        <v>20</v>
+        <v>36.363636363636</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1494,7 +1494,7 @@
         <v>0</v>
       </c>
       <c r="L29" s="13" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M29" s="15">
         <v>100</v>
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
@@ -1535,7 +1535,7 @@
         <v>-50</v>
       </c>
       <c r="L30" s="13" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M30" s="15">
         <v>0</v>
@@ -1548,14 +1548,14 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
@@ -1579,10 +1579,10 @@
         <v>-66.666666666666</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="L33" s="15">
         <v>-50</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C41" s="14">
         <v>1604</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14">
         <v>619</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14">
         <v>1345</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C44" s="14">
         <v>588</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C45" s="14">
         <v>1169</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C46" s="17">
         <v>5392</v>

--- a/data/source/weekly/cs-en-us-090pct.xlsx
+++ b/data/source/weekly/cs-en-us-090pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -202,6 +202,9 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -224,9 +227,6 @@
   </si>
   <si>
     <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Housing</t>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -890,25 +890,25 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
         <v>4</v>
@@ -920,7 +920,7 @@
         <v>33.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M15" s="15">
         <v>300</v>
@@ -931,253 +931,253 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E16" s="15">
-        <v>-66.666666666666</v>
+        <v>-62.5</v>
       </c>
       <c r="F16" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G16" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H16" s="15">
-        <v>-31.25</v>
+        <v>-35</v>
       </c>
       <c r="I16" s="14">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J16" s="14">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="K16" s="15">
-        <v>-2.777777777777</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="L16" s="15">
-        <v>6.060606060606</v>
+        <v>11.764705882352</v>
       </c>
       <c r="M16" s="15">
-        <v>-39.655172413793</v>
+        <v>-40.625</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.274509803921</v>
+        <v>-86.805555555555</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
         <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>-33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G17" s="14">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H17" s="15">
-        <v>-20.833333333333</v>
+        <v>-25</v>
       </c>
       <c r="I17" s="14">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="J17" s="14">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K17" s="15">
-        <v>7.142857142857</v>
+        <v>10.169491525423</v>
       </c>
       <c r="L17" s="15">
-        <v>7.142857142857</v>
+        <v>10.169491525423</v>
       </c>
       <c r="M17" s="15">
-        <v>76.470588235294</v>
+        <v>80.555555555555</v>
       </c>
       <c r="N17" s="15">
-        <v>-43.925233644859</v>
+        <v>-42.477876106194</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="F18" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G18" s="14">
         <v>18</v>
       </c>
       <c r="H18" s="15">
-        <v>44.444444444444</v>
+        <v>55.555555555555</v>
       </c>
       <c r="I18" s="14">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="J18" s="14">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K18" s="15">
-        <v>56.603773584905</v>
+        <v>55.172413793103</v>
       </c>
       <c r="L18" s="15">
-        <v>0</v>
+        <v>-1.098901098901</v>
       </c>
       <c r="M18" s="15">
-        <v>3.75</v>
+        <v>8.433734939759</v>
       </c>
       <c r="N18" s="15">
-        <v>-69.708029197080</v>
+        <v>-69.387755102040</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D19" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E19" s="15">
-        <v>7.142857142857</v>
+        <v>41.666666666666</v>
       </c>
       <c r="F19" s="14">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="G19" s="14">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H19" s="15">
-        <v>-12</v>
+        <v>12.244897959183</v>
       </c>
       <c r="I19" s="14">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="J19" s="14">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="K19" s="15">
-        <v>5.223880597014</v>
+        <v>10.273972602739</v>
       </c>
       <c r="L19" s="15">
-        <v>-16.071428571428</v>
+        <v>-9.039548022598</v>
       </c>
       <c r="M19" s="15">
-        <v>65.882352941176</v>
+        <v>67.708333333333</v>
       </c>
       <c r="N19" s="15">
-        <v>56.666666666666</v>
+        <v>57.843137254902</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
         <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="F20" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G20" s="14">
         <v>5</v>
       </c>
       <c r="H20" s="15">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="I20" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J20" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K20" s="15">
-        <v>42.857142857142</v>
+        <v>50</v>
       </c>
       <c r="L20" s="15">
-        <v>30.434782608695</v>
+        <v>32</v>
       </c>
       <c r="M20" s="15">
-        <v>-14.285714285714</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="N20" s="15">
-        <v>-83.240223463687</v>
+        <v>-83.248730964467</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D21" s="17">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E21" s="18">
-        <v>10.714285714285</v>
+        <v>24.137931034482</v>
       </c>
       <c r="F21" s="17">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="G21" s="17">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H21" s="18">
-        <v>2.586206896551</v>
+        <v>13.043478260869</v>
       </c>
       <c r="I21" s="17">
-        <v>353</v>
+        <v>391</v>
       </c>
       <c r="J21" s="17">
-        <v>305</v>
+        <v>334</v>
       </c>
       <c r="K21" s="18">
-        <v>15.737704918032</v>
+        <v>17.065868263473</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.814713896457</v>
+        <v>-0.255102040816</v>
       </c>
       <c r="M21" s="18">
-        <v>20.068027210884</v>
+        <v>22.1875</v>
       </c>
       <c r="N21" s="18">
-        <v>-61.504907306434</v>
+        <v>-61.171797418073</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>20</v>
@@ -1192,69 +1192,69 @@
         <v>1</v>
       </c>
       <c r="G22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="14">
         <v>8</v>
       </c>
       <c r="J22" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K22" s="15">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="L22" s="15">
         <v>33.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E23" s="15">
-        <v>-100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F23" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G23" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H23" s="15">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="I23" s="14">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J23" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K23" s="15">
-        <v>15.151515151515</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L23" s="15">
-        <v>-2.564102564102</v>
+        <v>7.317073170731</v>
       </c>
       <c r="M23" s="15">
-        <v>46.153846153846</v>
+        <v>62.962962962963</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D24" s="14">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E24" s="15">
-        <v>0</v>
+        <v>114.285714285714</v>
       </c>
       <c r="F24" s="14">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G24" s="14">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H24" s="15">
-        <v>-1.219512195121</v>
+        <v>18.75</v>
       </c>
       <c r="I24" s="14">
-        <v>270</v>
+        <v>301</v>
       </c>
       <c r="J24" s="14">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="K24" s="15">
-        <v>14.893617021276</v>
+        <v>20.883534136546</v>
       </c>
       <c r="L24" s="15">
-        <v>11.111111111111</v>
+        <v>17.120622568093</v>
       </c>
       <c r="M24" s="15">
-        <v>9.756097560975</v>
+        <v>12.734082397003</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
         <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>-14.285714285714</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F25" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G25" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H25" s="15">
-        <v>-27.272727272727</v>
+        <v>-40</v>
       </c>
       <c r="I25" s="14">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J25" s="14">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="K25" s="15">
-        <v>12.162162162162</v>
+        <v>6.172839506172</v>
       </c>
       <c r="L25" s="15">
-        <v>-3.488372093023</v>
+        <v>-5.494505494505</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,63 +1344,63 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="F26" s="14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G26" s="14">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H26" s="15">
-        <v>18.518518518518</v>
+        <v>56.521739130434</v>
       </c>
       <c r="I26" s="14">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="J26" s="14">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="K26" s="15">
-        <v>21.621621621621</v>
+        <v>29.487179487179</v>
       </c>
       <c r="L26" s="15">
-        <v>-27.419354838709</v>
+        <v>-24.060150375939</v>
       </c>
       <c r="M26" s="15">
-        <v>-4.255319148936</v>
+        <v>-0.980392156862</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>0</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
         <v>4</v>
@@ -1412,36 +1412,36 @@
         <v>33.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>3</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
         <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I28" s="14">
         <v>15</v>
@@ -1453,95 +1453,95 @@
         <v>25</v>
       </c>
       <c r="L28" s="15">
-        <v>36.363636363636</v>
+        <v>25</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29" s="14">
         <v>2</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L29" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="M29" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N29" s="15">
-        <v>-88.888888888888</v>
+        <v>-84.210526315789</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="14">
         <v>2</v>
       </c>
       <c r="K30" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L30" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="M30" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N30" s="15">
-        <v>-94.444444444444</v>
+        <v>-89.473684210526</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,16 +1555,16 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
       </c>
       <c r="G31" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H31" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I31" s="14">
         <v>2</v>
@@ -1576,13 +1576,13 @@
         <v>-60</v>
       </c>
       <c r="L31" s="15">
-        <v>-66.666666666666</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="L33" s="15">
         <v>-50</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>43</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C41" s="14">
         <v>1604</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14">
         <v>619</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C43" s="14">
         <v>1345</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44" s="14">
         <v>588</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" s="14">
         <v>1169</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C46" s="17">
         <v>5392</v>

--- a/data/source/weekly/cs-en-us-090pct.xlsx
+++ b/data/source/weekly/cs-en-us-090pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -860,32 +860,32 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="14">
         <v>2</v>
       </c>
       <c r="H14" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>20</v>
+        <v>-50</v>
+      </c>
+      <c r="I14" s="14">
+        <v>1</v>
       </c>
       <c r="J14" s="14">
         <v>2</v>
       </c>
       <c r="K14" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="L14" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="M14" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-100</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -895,29 +895,29 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
+        <v>1</v>
+      </c>
+      <c r="G15" s="14">
         <v>2</v>
       </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
         <v>4</v>
       </c>
       <c r="J15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L15" s="15">
         <v>0</v>
@@ -926,7 +926,7 @@
         <v>300</v>
       </c>
       <c r="N15" s="15">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>1</v>
+      </c>
+      <c r="D16" s="14">
         <v>3</v>
       </c>
-      <c r="D16" s="14">
-        <v>8</v>
-      </c>
       <c r="E16" s="15">
-        <v>-62.5</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="14">
         <v>13</v>
@@ -952,22 +952,22 @@
         <v>-35</v>
       </c>
       <c r="I16" s="14">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J16" s="14">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K16" s="15">
-        <v>-13.636363636363</v>
+        <v>-14.893617021276</v>
       </c>
       <c r="L16" s="15">
-        <v>11.764705882352</v>
+        <v>5.263157894736</v>
       </c>
       <c r="M16" s="15">
-        <v>-40.625</v>
+        <v>-47.368421052631</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.805555555555</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>66.666666666666</v>
+        <v>200</v>
       </c>
       <c r="F17" s="14">
+        <v>22</v>
+      </c>
+      <c r="G17" s="14">
         <v>15</v>
       </c>
-      <c r="G17" s="14">
-        <v>20</v>
-      </c>
       <c r="H17" s="15">
-        <v>-25</v>
+        <v>46.666666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="J17" s="14">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="K17" s="15">
-        <v>10.169491525423</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L17" s="15">
-        <v>10.169491525423</v>
+        <v>28.333333333333</v>
       </c>
       <c r="M17" s="15">
-        <v>80.555555555555</v>
+        <v>97.435897435897</v>
       </c>
       <c r="N17" s="15">
-        <v>-42.477876106194</v>
+        <v>-35.833333333333</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
         <v>7</v>
       </c>
-      <c r="D18" s="14">
-        <v>5</v>
-      </c>
       <c r="E18" s="15">
-        <v>40</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="F18" s="14">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G18" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H18" s="15">
-        <v>55.555555555555</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J18" s="14">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="K18" s="15">
-        <v>55.172413793103</v>
+        <v>41.538461538461</v>
       </c>
       <c r="L18" s="15">
-        <v>-1.098901098901</v>
+        <v>-6.122448979591</v>
       </c>
       <c r="M18" s="15">
-        <v>8.433734939759</v>
+        <v>4.545454545454</v>
       </c>
       <c r="N18" s="15">
-        <v>-69.387755102040</v>
+        <v>-70.977917981072</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>21</v>
+      </c>
+      <c r="D19" s="14">
         <v>17</v>
       </c>
-      <c r="D19" s="14">
-        <v>12</v>
-      </c>
       <c r="E19" s="15">
-        <v>41.666666666666</v>
+        <v>23.529411764705</v>
       </c>
       <c r="F19" s="14">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="G19" s="14">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H19" s="15">
-        <v>12.244897959183</v>
+        <v>30.188679245283</v>
       </c>
       <c r="I19" s="14">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="J19" s="14">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="K19" s="15">
-        <v>10.273972602739</v>
+        <v>12.269938650306</v>
       </c>
       <c r="L19" s="15">
-        <v>-9.039548022598</v>
+        <v>-5.670103092783</v>
       </c>
       <c r="M19" s="15">
-        <v>67.708333333333</v>
+        <v>69.444444444444</v>
       </c>
       <c r="N19" s="15">
-        <v>57.843137254902</v>
+        <v>67.889908256880</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>1</v>
+      </c>
+      <c r="D20" s="14">
         <v>4</v>
       </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
       <c r="E20" s="15">
-        <v>300</v>
+        <v>-75</v>
       </c>
       <c r="F20" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G20" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H20" s="15">
-        <v>240</v>
+        <v>62.5</v>
       </c>
       <c r="I20" s="14">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J20" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K20" s="15">
-        <v>50</v>
+        <v>30.769230769230</v>
       </c>
       <c r="L20" s="15">
-        <v>32</v>
+        <v>17.241379310344</v>
       </c>
       <c r="M20" s="15">
-        <v>-15.384615384615</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="N20" s="15">
-        <v>-83.248730964467</v>
+        <v>-84.112149532710</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>37</v>
+      </c>
+      <c r="D21" s="17">
         <v>36</v>
       </c>
-      <c r="D21" s="17">
-        <v>29</v>
-      </c>
       <c r="E21" s="18">
-        <v>24.137931034482</v>
+        <v>2.777777777777</v>
       </c>
       <c r="F21" s="17">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="G21" s="17">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H21" s="18">
-        <v>13.043478260869</v>
+        <v>16.239316239316</v>
       </c>
       <c r="I21" s="17">
-        <v>391</v>
+        <v>431</v>
       </c>
       <c r="J21" s="17">
-        <v>334</v>
+        <v>370</v>
       </c>
       <c r="K21" s="18">
-        <v>17.065868263473</v>
+        <v>16.486486486486</v>
       </c>
       <c r="L21" s="18">
-        <v>-0.255102040816</v>
+        <v>1.411764705882</v>
       </c>
       <c r="M21" s="18">
-        <v>22.1875</v>
+        <v>21.408450704225</v>
       </c>
       <c r="N21" s="18">
-        <v>-61.171797418073</v>
+        <v>-60.639269406392</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,11 +1182,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
         <v>1</v>
@@ -1207,10 +1207,10 @@
         <v>0</v>
       </c>
       <c r="L22" s="15">
-        <v>33.333333333333</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M22" s="15">
-        <v>-11.111111111111</v>
+        <v>-20</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1224,34 +1224,34 @@
         <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
         <v>15</v>
       </c>
       <c r="G23" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H23" s="15">
-        <v>50</v>
+        <v>36.363636363636</v>
       </c>
       <c r="I23" s="14">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J23" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K23" s="15">
-        <v>22.222222222222</v>
+        <v>20</v>
       </c>
       <c r="L23" s="15">
-        <v>7.317073170731</v>
+        <v>11.627906976744</v>
       </c>
       <c r="M23" s="15">
-        <v>62.962962962963</v>
+        <v>60</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D24" s="14">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15">
-        <v>114.285714285714</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="F24" s="14">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G24" s="14">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H24" s="15">
-        <v>18.75</v>
+        <v>25.333333333333</v>
       </c>
       <c r="I24" s="14">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="J24" s="14">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="K24" s="15">
-        <v>20.883534136546</v>
+        <v>18.283582089552</v>
       </c>
       <c r="L24" s="15">
-        <v>17.120622568093</v>
+        <v>15.272727272727</v>
       </c>
       <c r="M24" s="15">
-        <v>12.734082397003</v>
+        <v>10.839160839160</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>-57.142857142857</v>
+        <v>50</v>
       </c>
       <c r="F25" s="14">
         <v>15</v>
       </c>
       <c r="G25" s="14">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H25" s="15">
-        <v>-40</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="I25" s="14">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J25" s="14">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K25" s="15">
-        <v>6.172839506172</v>
+        <v>7.228915662650</v>
       </c>
       <c r="L25" s="15">
-        <v>-5.494505494505</v>
+        <v>-11.881188118811</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D26" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E26" s="15">
-        <v>175</v>
+        <v>333.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G26" s="14">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H26" s="15">
-        <v>56.521739130434</v>
+        <v>90</v>
       </c>
       <c r="I26" s="14">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="J26" s="14">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K26" s="15">
-        <v>29.487179487179</v>
+        <v>40.740740740740</v>
       </c>
       <c r="L26" s="15">
-        <v>-24.060150375939</v>
+        <v>-23.489932885906</v>
       </c>
       <c r="M26" s="15">
-        <v>-0.980392156862</v>
+        <v>3.636363636363</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
+        <v>5</v>
+      </c>
+      <c r="J27" s="14">
         <v>4</v>
       </c>
-      <c r="J27" s="14">
-        <v>3</v>
-      </c>
       <c r="K27" s="15">
-        <v>33.333333333333</v>
+        <v>25</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,14 +1425,14 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
         <v>4</v>
@@ -1444,16 +1444,16 @@
         <v>33.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J28" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K28" s="15">
-        <v>25</v>
+        <v>23.076923076923</v>
       </c>
       <c r="L28" s="15">
-        <v>25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1467,7 +1467,7 @@
         <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1476,31 +1476,31 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I29" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J29" s="14">
         <v>2</v>
       </c>
       <c r="K29" s="15">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M29" s="15">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="N29" s="15">
-        <v>-84.210526315789</v>
+        <v>-76.190476190476</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1517,31 +1517,31 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30" s="14">
         <v>2</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M30" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N30" s="15">
-        <v>-89.473684210526</v>
+        <v>-85</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1558,25 +1558,25 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>1</v>
-      </c>
-      <c r="G31" s="14">
         <v>2</v>
       </c>
-      <c r="H31" s="15">
-        <v>-50</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J31" s="14">
         <v>5</v>
       </c>
       <c r="K31" s="15">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="L31" s="15">
-        <v>-71.428571428571</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-090pct.xlsx
+++ b/data/source/weekly/cs-en-us-090pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -864,10 +864,10 @@
         <v>1</v>
       </c>
       <c r="G14" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
@@ -920,13 +920,13 @@
         <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="M15" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="N15" s="15">
-        <v>-55.555555555555</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G16" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H16" s="15">
-        <v>-35</v>
+        <v>-57.894736842105</v>
       </c>
       <c r="I16" s="14">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J16" s="14">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K16" s="15">
-        <v>-14.893617021276</v>
+        <v>-16.326530612244</v>
       </c>
       <c r="L16" s="15">
-        <v>5.263157894736</v>
+        <v>-6.818181818181</v>
       </c>
       <c r="M16" s="15">
-        <v>-47.368421052631</v>
+        <v>-50</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.5</v>
+        <v>-87.797619047619</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="F17" s="14">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G17" s="14">
         <v>15</v>
       </c>
       <c r="H17" s="15">
-        <v>46.666666666666</v>
+        <v>93.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="J17" s="14">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="K17" s="15">
-        <v>22.222222222222</v>
+        <v>27.941176470588</v>
       </c>
       <c r="L17" s="15">
-        <v>28.333333333333</v>
+        <v>33.846153846153</v>
       </c>
       <c r="M17" s="15">
-        <v>97.435897435897</v>
+        <v>89.130434782608</v>
       </c>
       <c r="N17" s="15">
-        <v>-35.833333333333</v>
+        <v>-35.074626865671</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-85.714285714285</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G18" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H18" s="15">
         <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J18" s="14">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="K18" s="15">
-        <v>41.538461538461</v>
+        <v>40.579710144927</v>
       </c>
       <c r="L18" s="15">
-        <v>-6.122448979591</v>
+        <v>-7.619047619047</v>
       </c>
       <c r="M18" s="15">
-        <v>4.545454545454</v>
+        <v>5.434782608695</v>
       </c>
       <c r="N18" s="15">
-        <v>-70.977917981072</v>
+        <v>-71.965317919075</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D19" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E19" s="15">
-        <v>23.529411764705</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G19" s="14">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H19" s="15">
-        <v>30.188679245283</v>
+        <v>20.689655172413</v>
       </c>
       <c r="I19" s="14">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="J19" s="14">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="K19" s="15">
-        <v>12.269938650306</v>
+        <v>10.112359550561</v>
       </c>
       <c r="L19" s="15">
-        <v>-5.670103092783</v>
+        <v>-5.769230769230</v>
       </c>
       <c r="M19" s="15">
-        <v>69.444444444444</v>
+        <v>70.434782608695</v>
       </c>
       <c r="N19" s="15">
-        <v>67.889908256880</v>
+        <v>68.965517241379</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>-75</v>
+        <v>100</v>
       </c>
       <c r="F20" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G20" s="14">
         <v>8</v>
       </c>
       <c r="H20" s="15">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="I20" s="14">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J20" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K20" s="15">
-        <v>30.769230769230</v>
+        <v>39.285714285714</v>
       </c>
       <c r="L20" s="15">
-        <v>17.241379310344</v>
+        <v>25.806451612903</v>
       </c>
       <c r="M20" s="15">
-        <v>-19.047619047619</v>
+        <v>-9.302325581395</v>
       </c>
       <c r="N20" s="15">
-        <v>-84.112149532710</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D21" s="17">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E21" s="18">
-        <v>2.777777777777</v>
+        <v>7.142857142857</v>
       </c>
       <c r="F21" s="17">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G21" s="17">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H21" s="18">
-        <v>16.239316239316</v>
+        <v>18.181818181818</v>
       </c>
       <c r="I21" s="17">
-        <v>431</v>
+        <v>465</v>
       </c>
       <c r="J21" s="17">
-        <v>370</v>
+        <v>398</v>
       </c>
       <c r="K21" s="18">
-        <v>16.486486486486</v>
+        <v>16.834170854271</v>
       </c>
       <c r="L21" s="18">
-        <v>1.411764705882</v>
+        <v>1.086956521739</v>
       </c>
       <c r="M21" s="18">
-        <v>21.408450704225</v>
+        <v>22.047244094488</v>
       </c>
       <c r="N21" s="18">
-        <v>-60.639269406392</v>
+        <v>-60.659898477157</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="C22" s="14">
+        <v>2</v>
+      </c>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>100</v>
       </c>
       <c r="F22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I22" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J22" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K22" s="15">
+        <v>11.111111111111</v>
+      </c>
+      <c r="L22" s="15">
+        <v>25</v>
+      </c>
+      <c r="M22" s="15">
         <v>0</v>
-      </c>
-      <c r="L22" s="15">
-        <v>14.285714285714</v>
-      </c>
-      <c r="M22" s="15">
-        <v>-20</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1224,34 +1224,34 @@
         <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F23" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G23" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H23" s="15">
-        <v>36.363636363636</v>
+        <v>40</v>
       </c>
       <c r="I23" s="14">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J23" s="14">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K23" s="15">
-        <v>20</v>
+        <v>23.809523809523</v>
       </c>
       <c r="L23" s="15">
-        <v>11.627906976744</v>
+        <v>15.555555555555</v>
       </c>
       <c r="M23" s="15">
-        <v>60</v>
+        <v>67.741935483871</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D24" s="14">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E24" s="15">
-        <v>-31.578947368421</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G24" s="14">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H24" s="15">
-        <v>25.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I24" s="14">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="J24" s="14">
-        <v>268</v>
+        <v>298</v>
       </c>
       <c r="K24" s="15">
-        <v>18.283582089552</v>
+        <v>11.744966442953</v>
       </c>
       <c r="L24" s="15">
-        <v>15.272727272727</v>
+        <v>13.265306122449</v>
       </c>
       <c r="M24" s="15">
-        <v>10.839160839160</v>
+        <v>7.419354838709</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15">
-        <v>50</v>
+        <v>-75</v>
       </c>
       <c r="F25" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G25" s="14">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H25" s="15">
-        <v>-21.052631578947</v>
+        <v>-45.833333333333</v>
       </c>
       <c r="I25" s="14">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J25" s="14">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="K25" s="15">
-        <v>7.228915662650</v>
+        <v>-1.098901098901</v>
       </c>
       <c r="L25" s="15">
-        <v>-11.881188118811</v>
+        <v>-20.353982300885</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>333.333333333333</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="F26" s="14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G26" s="14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H26" s="15">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="I26" s="14">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="J26" s="14">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K26" s="15">
-        <v>40.740740740740</v>
+        <v>35.869565217391</v>
       </c>
       <c r="L26" s="15">
-        <v>-23.489932885906</v>
+        <v>-19.871794871794</v>
       </c>
       <c r="M26" s="15">
-        <v>3.636363636363</v>
+        <v>2.459016393442</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,14 +1384,14 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>0</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
@@ -1412,7 +1412,7 @@
         <v>25</v>
       </c>
       <c r="L27" s="15">
-        <v>25</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,32 +1425,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
         <v>4</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="I28" s="14">
         <v>16</v>
       </c>
       <c r="J28" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K28" s="15">
-        <v>23.076923076923</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L28" s="15">
         <v>33.333333333333</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>2</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1478,11 +1478,11 @@
       <c r="F29" s="14">
         <v>3</v>
       </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>200</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="14">
         <v>5</v>
@@ -1507,8 +1507,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1519,11 +1519,11 @@
       <c r="F30" s="14">
         <v>2</v>
       </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>100</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="14">
         <v>3</v>
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>-40</v>
       </c>
       <c r="L31" s="15">
-        <v>-57.142857142857</v>
+        <v>-62.5</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-090pct.xlsx
+++ b/data/source/weekly/cs-en-us-090pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -863,11 +863,11 @@
       <c r="F14" s="14">
         <v>1</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>0</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,28 +905,28 @@
         <v>1</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15" s="14">
         <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L15" s="15">
-        <v>-20</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M15" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="N15" s="15">
-        <v>-60</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G16" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H16" s="15">
-        <v>-57.894736842105</v>
+        <v>-43.75</v>
       </c>
       <c r="I16" s="14">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J16" s="14">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K16" s="15">
-        <v>-16.326530612244</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="L16" s="15">
-        <v>-6.818181818181</v>
+        <v>-6.382978723404</v>
       </c>
       <c r="M16" s="15">
-        <v>-50</v>
+        <v>-50.561797752809</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.797619047619</v>
+        <v>-87.605633802816</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E17" s="15">
-        <v>60</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G17" s="14">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H17" s="15">
-        <v>93.333333333333</v>
+        <v>12.5</v>
       </c>
       <c r="I17" s="14">
         <v>87</v>
       </c>
       <c r="J17" s="14">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="K17" s="15">
-        <v>27.941176470588</v>
+        <v>8.75</v>
       </c>
       <c r="L17" s="15">
-        <v>33.846153846153</v>
+        <v>16</v>
       </c>
       <c r="M17" s="15">
-        <v>89.130434782608</v>
+        <v>50</v>
       </c>
       <c r="N17" s="15">
-        <v>-35.074626865671</v>
+        <v>-39.160839160839</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="F18" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G18" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="I18" s="14">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="J18" s="14">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="K18" s="15">
-        <v>40.579710144927</v>
+        <v>35.135135135135</v>
       </c>
       <c r="L18" s="15">
-        <v>-7.619047619047</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="M18" s="15">
-        <v>5.434782608695</v>
+        <v>-0.990099009900</v>
       </c>
       <c r="N18" s="15">
-        <v>-71.965317919075</v>
+        <v>-72.602739726027</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>13</v>
       </c>
       <c r="D19" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>-13.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G19" s="14">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H19" s="15">
-        <v>20.689655172413</v>
+        <v>14.035087719298</v>
       </c>
       <c r="I19" s="14">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="J19" s="14">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="K19" s="15">
-        <v>10.112359550561</v>
+        <v>9.424083769633</v>
       </c>
       <c r="L19" s="15">
-        <v>-5.769230769230</v>
+        <v>-4.128440366972</v>
       </c>
       <c r="M19" s="15">
-        <v>70.434782608695</v>
+        <v>74.166666666666</v>
       </c>
       <c r="N19" s="15">
-        <v>68.965517241379</v>
+        <v>63.28125</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="F20" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G20" s="14">
         <v>8</v>
       </c>
       <c r="H20" s="15">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="I20" s="14">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J20" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K20" s="15">
-        <v>39.285714285714</v>
+        <v>48.275862068965</v>
       </c>
       <c r="L20" s="15">
-        <v>25.806451612903</v>
+        <v>22.857142857142</v>
       </c>
       <c r="M20" s="15">
-        <v>-9.302325581395</v>
+        <v>-10.416666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-83.333333333333</v>
+        <v>-82.661290322580</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,54 +1139,54 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D21" s="17">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E21" s="18">
-        <v>7.142857142857</v>
+        <v>-20.588235294117</v>
       </c>
       <c r="F21" s="17">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="G21" s="17">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="H21" s="18">
-        <v>18.181818181818</v>
+        <v>5.511811023622</v>
       </c>
       <c r="I21" s="17">
-        <v>465</v>
+        <v>489</v>
       </c>
       <c r="J21" s="17">
-        <v>398</v>
+        <v>432</v>
       </c>
       <c r="K21" s="18">
-        <v>16.834170854271</v>
+        <v>13.194444444444</v>
       </c>
       <c r="L21" s="18">
-        <v>1.086956521739</v>
+        <v>-1.212121212121</v>
       </c>
       <c r="M21" s="18">
-        <v>22.047244094488</v>
+        <v>16.706443914081</v>
       </c>
       <c r="N21" s="18">
-        <v>-60.659898477157</v>
+        <v>-61.035856573705</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>2</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="14">
         <v>1</v>
       </c>
       <c r="E22" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>2</v>
@@ -1201,16 +1201,16 @@
         <v>10</v>
       </c>
       <c r="J22" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K22" s="15">
+        <v>0</v>
+      </c>
+      <c r="L22" s="15">
         <v>11.111111111111</v>
       </c>
-      <c r="L22" s="15">
-        <v>25</v>
-      </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,10 +1221,10 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
         <v>100</v>
@@ -1239,19 +1239,19 @@
         <v>40</v>
       </c>
       <c r="I23" s="14">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J23" s="14">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K23" s="15">
-        <v>23.809523809523</v>
+        <v>25.581395348837</v>
       </c>
       <c r="L23" s="15">
-        <v>15.555555555555</v>
+        <v>14.893617021276</v>
       </c>
       <c r="M23" s="15">
-        <v>67.741935483871</v>
+        <v>54.285714285714</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D24" s="14">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E24" s="15">
-        <v>-46.666666666666</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F24" s="14">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G24" s="14">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H24" s="15">
         <v>0</v>
       </c>
       <c r="I24" s="14">
-        <v>333</v>
+        <v>352</v>
       </c>
       <c r="J24" s="14">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="K24" s="15">
-        <v>11.744966442953</v>
+        <v>11.392405063291</v>
       </c>
       <c r="L24" s="15">
-        <v>13.265306122449</v>
+        <v>12.101910828025</v>
       </c>
       <c r="M24" s="15">
-        <v>7.419354838709</v>
+        <v>5.389221556886</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>-75</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F25" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G25" s="14">
         <v>24</v>
       </c>
       <c r="H25" s="15">
-        <v>-45.833333333333</v>
+        <v>-50</v>
       </c>
       <c r="I25" s="14">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J25" s="14">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="K25" s="15">
-        <v>-1.098901098901</v>
+        <v>-3.061224489795</v>
       </c>
       <c r="L25" s="15">
-        <v>-20.353982300885</v>
+        <v>-22.764227642276</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E26" s="15">
-        <v>-9.090909090909</v>
+        <v>100</v>
       </c>
       <c r="F26" s="14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G26" s="14">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H26" s="15">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="I26" s="14">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="J26" s="14">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K26" s="15">
-        <v>35.869565217391</v>
+        <v>39.583333333333</v>
       </c>
       <c r="L26" s="15">
-        <v>-19.871794871794</v>
+        <v>-23.428571428571</v>
       </c>
       <c r="M26" s="15">
-        <v>2.459016393442</v>
+        <v>3.875968992248</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1397,22 +1397,22 @@
         <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J27" s="14">
         <v>4</v>
       </c>
       <c r="K27" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="L27" s="15">
-        <v>-16.666666666666</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,20 +1428,20 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
         <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F28" s="14">
-        <v>4</v>
       </c>
       <c r="G28" s="14">
         <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="I28" s="14">
         <v>16</v>
@@ -1453,7 +1453,7 @@
         <v>14.285714285714</v>
       </c>
       <c r="L28" s="15">
-        <v>33.333333333333</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1497,10 +1497,10 @@
         <v>21</v>
       </c>
       <c r="M29" s="15">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="N29" s="15">
-        <v>-76.190476190476</v>
+        <v>-77.272727272727</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1538,10 +1538,10 @@
         <v>21</v>
       </c>
       <c r="M30" s="15">
-        <v>200</v>
+        <v>-25</v>
       </c>
       <c r="N30" s="15">
-        <v>-85</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,32 +1551,32 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>8</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="14">
+        <v>8</v>
+      </c>
+      <c r="H31" s="15">
+        <v>-87.5</v>
       </c>
       <c r="I31" s="14">
         <v>3</v>
       </c>
       <c r="J31" s="14">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="K31" s="15">
-        <v>-40</v>
+        <v>-76.923076923076</v>
       </c>
       <c r="L31" s="15">
-        <v>-62.5</v>
+        <v>-70</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1610,32 +1610,32 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>21</v>
+      <c r="G33" s="14">
+        <v>1</v>
+      </c>
+      <c r="H33" s="15">
+        <v>-100</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
       </c>
-      <c r="J33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" s="13" t="s">
-        <v>21</v>
+      <c r="J33" s="14">
+        <v>1</v>
+      </c>
+      <c r="K33" s="15">
+        <v>0</v>
       </c>
       <c r="L33" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-090pct.xlsx
+++ b/data/source/weekly/cs-en-us-090pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -885,15 +885,15 @@
         <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-83.333333333333</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -920,7 +920,7 @@
         <v>25</v>
       </c>
       <c r="L15" s="15">
-        <v>-16.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M15" s="15">
         <v>150</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="14">
         <v>9</v>
       </c>
       <c r="G16" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H16" s="15">
-        <v>-43.75</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="I16" s="14">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J16" s="14">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="K16" s="15">
-        <v>-15.384615384615</v>
+        <v>-17.241379310344</v>
       </c>
       <c r="L16" s="15">
-        <v>-6.382978723404</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="M16" s="15">
-        <v>-50.561797752809</v>
+        <v>-51.020408163265</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.605633802816</v>
+        <v>-87.434554973822</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E17" s="15">
-        <v>-83.333333333333</v>
+        <v>-62.5</v>
       </c>
       <c r="F17" s="14">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G17" s="14">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H17" s="15">
-        <v>12.5</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="I17" s="14">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="J17" s="14">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K17" s="15">
-        <v>8.75</v>
+        <v>3.409090909090</v>
       </c>
       <c r="L17" s="15">
-        <v>16</v>
+        <v>10.975609756097</v>
       </c>
       <c r="M17" s="15">
-        <v>50</v>
+        <v>54.237288135593</v>
       </c>
       <c r="N17" s="15">
-        <v>-39.160839160839</v>
+        <v>-41.290322580645</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>3</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>-40</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H18" s="15">
-        <v>-19.047619047619</v>
+        <v>-59.090909090909</v>
       </c>
       <c r="I18" s="14">
         <v>100</v>
       </c>
       <c r="J18" s="14">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="K18" s="15">
-        <v>35.135135135135</v>
+        <v>25</v>
       </c>
       <c r="L18" s="15">
-        <v>-10.714285714285</v>
+        <v>-17.355371900826</v>
       </c>
       <c r="M18" s="15">
-        <v>-0.990099009900</v>
+        <v>-9.909909909909</v>
       </c>
       <c r="N18" s="15">
-        <v>-72.602739726027</v>
+        <v>-73.821989528795</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="F19" s="14">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G19" s="14">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H19" s="15">
-        <v>14.035087719298</v>
+        <v>-1.694915254237</v>
       </c>
       <c r="I19" s="14">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="J19" s="14">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="K19" s="15">
-        <v>9.424083769633</v>
+        <v>7.317073170731</v>
       </c>
       <c r="L19" s="15">
-        <v>-4.128440366972</v>
+        <v>-3.083700440528</v>
       </c>
       <c r="M19" s="15">
-        <v>74.166666666666</v>
+        <v>76</v>
       </c>
       <c r="N19" s="15">
-        <v>63.28125</v>
+        <v>60.583941605839</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G20" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H20" s="15">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="I20" s="14">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J20" s="14">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K20" s="15">
-        <v>48.275862068965</v>
+        <v>41.176470588235</v>
       </c>
       <c r="L20" s="15">
-        <v>22.857142857142</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M20" s="15">
-        <v>-10.416666666666</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="N20" s="15">
-        <v>-82.661290322580</v>
+        <v>-81.467181467181</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D21" s="17">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E21" s="18">
-        <v>-20.588235294117</v>
+        <v>-41.025641025641</v>
       </c>
       <c r="F21" s="17">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="G21" s="17">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="H21" s="18">
-        <v>5.511811023622</v>
+        <v>-13.868613138686</v>
       </c>
       <c r="I21" s="17">
-        <v>489</v>
+        <v>513</v>
       </c>
       <c r="J21" s="17">
-        <v>432</v>
+        <v>471</v>
       </c>
       <c r="K21" s="18">
-        <v>13.194444444444</v>
+        <v>8.917197452229</v>
       </c>
       <c r="L21" s="18">
-        <v>-1.212121212121</v>
+        <v>-2.656546489563</v>
       </c>
       <c r="M21" s="18">
-        <v>16.706443914081</v>
+        <v>14.508928571428</v>
       </c>
       <c r="N21" s="18">
-        <v>-61.035856573705</v>
+        <v>-61.515378844711</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="14">
+        <v>2</v>
+      </c>
+      <c r="D22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
+        <v>4</v>
+      </c>
+      <c r="G22" s="14">
         <v>2</v>
       </c>
-      <c r="G22" s="14">
-        <v>3</v>
-      </c>
       <c r="H22" s="15">
-        <v>-33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="I22" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J22" s="14">
         <v>10</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L22" s="15">
-        <v>11.111111111111</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>-9.090909090909</v>
+        <v>9.090909090909</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E23" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F23" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G23" s="14">
         <v>10</v>
       </c>
       <c r="H23" s="15">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I23" s="14">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="J23" s="14">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K23" s="15">
-        <v>25.581395348837</v>
+        <v>28.260869565217</v>
       </c>
       <c r="L23" s="15">
-        <v>14.893617021276</v>
+        <v>18</v>
       </c>
       <c r="M23" s="15">
-        <v>54.285714285714</v>
+        <v>55.263157894736</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D24" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E24" s="15">
-        <v>11.111111111111</v>
+        <v>82.352941176470</v>
       </c>
       <c r="F24" s="14">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G24" s="14">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H24" s="15">
-        <v>0</v>
+        <v>-5.952380952380</v>
       </c>
       <c r="I24" s="14">
-        <v>352</v>
+        <v>383</v>
       </c>
       <c r="J24" s="14">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="K24" s="15">
-        <v>11.392405063291</v>
+        <v>15.015015015015</v>
       </c>
       <c r="L24" s="15">
-        <v>12.101910828025</v>
+        <v>17.846153846153</v>
       </c>
       <c r="M24" s="15">
-        <v>5.389221556886</v>
+        <v>8.192090395480</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>-28.571428571428</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G25" s="14">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H25" s="15">
-        <v>-50</v>
+        <v>-35</v>
       </c>
       <c r="I25" s="14">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J25" s="14">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K25" s="15">
-        <v>-3.061224489795</v>
+        <v>-1.980198019801</v>
       </c>
       <c r="L25" s="15">
-        <v>-22.764227642276</v>
+        <v>-22.65625</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D26" s="14">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E26" s="15">
-        <v>100</v>
+        <v>35.714285714285</v>
       </c>
       <c r="F26" s="14">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G26" s="14">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="H26" s="15">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="I26" s="14">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="J26" s="14">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="K26" s="15">
-        <v>39.583333333333</v>
+        <v>39.090909090909</v>
       </c>
       <c r="L26" s="15">
-        <v>-23.428571428571</v>
+        <v>-16.847826086956</v>
       </c>
       <c r="M26" s="15">
-        <v>3.875968992248</v>
+        <v>10.869565217391</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1412,7 +1412,7 @@
         <v>50</v>
       </c>
       <c r="L27" s="15">
-        <v>-14.285714285714</v>
+        <v>-25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,8 +1425,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1435,25 +1435,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="14">
         <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J28" s="14">
         <v>14</v>
       </c>
       <c r="K28" s="15">
-        <v>14.285714285714</v>
+        <v>21.428571428571</v>
       </c>
       <c r="L28" s="15">
-        <v>14.285714285714</v>
+        <v>21.428571428571</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1476,7 +1476,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1500,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="N29" s="15">
-        <v>-77.272727272727</v>
+        <v>-79.166666666666</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1517,7 +1517,7 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1541,42 +1541,42 @@
         <v>-25</v>
       </c>
       <c r="N30" s="15">
-        <v>-85.714285714285</v>
+        <v>-86.956521739130</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="14">
+        <v>4</v>
+      </c>
+      <c r="D31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>8</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G31" s="14">
         <v>8</v>
       </c>
       <c r="H31" s="15">
-        <v>-87.5</v>
+        <v>-50</v>
       </c>
       <c r="I31" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J31" s="14">
         <v>13</v>
       </c>
       <c r="K31" s="15">
-        <v>-76.923076923076</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="L31" s="15">
-        <v>-70</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1610,11 +1610,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-090pct.xlsx
+++ b/data/source/weekly/cs-en-us-090pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="14">
-        <v>1</v>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -904,11 +904,11 @@
       <c r="F15" s="14">
         <v>1</v>
       </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
-      <c r="H15" s="15">
-        <v>0</v>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="14">
         <v>5</v>
@@ -920,13 +920,13 @@
         <v>25</v>
       </c>
       <c r="L15" s="15">
-        <v>-28.571428571428</v>
+        <v>-37.5</v>
       </c>
       <c r="M15" s="15">
         <v>150</v>
       </c>
       <c r="N15" s="15">
-        <v>-50</v>
+        <v>-61.538461538461</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>-33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="14">
         <v>9</v>
@@ -952,22 +952,22 @@
         <v>-35.714285714285</v>
       </c>
       <c r="I16" s="14">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J16" s="14">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K16" s="15">
-        <v>-17.241379310344</v>
+        <v>-19.672131147541</v>
       </c>
       <c r="L16" s="15">
-        <v>-7.692307692307</v>
+        <v>-9.259259259259</v>
       </c>
       <c r="M16" s="15">
-        <v>-51.020408163265</v>
+        <v>-51.485148514851</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.434554973822</v>
+        <v>-87.657430730478</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>-62.5</v>
+        <v>-60</v>
       </c>
       <c r="F17" s="14">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G17" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H17" s="15">
-        <v>-13.793103448275</v>
+        <v>-43.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="J17" s="14">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="K17" s="15">
-        <v>3.409090909090</v>
+        <v>2.150537634408</v>
       </c>
       <c r="L17" s="15">
-        <v>10.975609756097</v>
+        <v>2.150537634408</v>
       </c>
       <c r="M17" s="15">
-        <v>54.237288135593</v>
+        <v>53.225806451612</v>
       </c>
       <c r="N17" s="15">
-        <v>-41.290322580645</v>
+        <v>-43.452380952380</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="F18" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G18" s="14">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H18" s="15">
-        <v>-59.090909090909</v>
+        <v>-57.894736842105</v>
       </c>
       <c r="I18" s="14">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J18" s="14">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="K18" s="15">
-        <v>25</v>
+        <v>20.238095238095</v>
       </c>
       <c r="L18" s="15">
-        <v>-17.355371900826</v>
+        <v>-20.472440944881</v>
       </c>
       <c r="M18" s="15">
-        <v>-9.909909909909</v>
+        <v>-11.403508771929</v>
       </c>
       <c r="N18" s="15">
-        <v>-73.821989528795</v>
+        <v>-74.812967581047</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D19" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>-21.428571428571</v>
+        <v>53.846153846153</v>
       </c>
       <c r="F19" s="14">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G19" s="14">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="H19" s="15">
-        <v>-1.694915254237</v>
+        <v>3.636363636363</v>
       </c>
       <c r="I19" s="14">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="J19" s="14">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="K19" s="15">
-        <v>7.317073170731</v>
+        <v>10.091743119266</v>
       </c>
       <c r="L19" s="15">
-        <v>-3.083700440528</v>
+        <v>-1.639344262295</v>
       </c>
       <c r="M19" s="15">
-        <v>76</v>
+        <v>73.913043478260</v>
       </c>
       <c r="N19" s="15">
-        <v>60.583941605839</v>
+        <v>63.265306122449</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
         <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="F20" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G20" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H20" s="15">
-        <v>25</v>
+        <v>30.769230769230</v>
       </c>
       <c r="I20" s="14">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J20" s="14">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="K20" s="15">
-        <v>41.176470588235</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>33.333333333333</v>
+        <v>36.842105263157</v>
       </c>
       <c r="M20" s="15">
-        <v>-7.692307692307</v>
+        <v>-3.703703703703</v>
       </c>
       <c r="N20" s="15">
-        <v>-81.467181467181</v>
+        <v>-81.560283687943</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,75 +1139,75 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D21" s="17">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E21" s="18">
-        <v>-41.025641025641</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="G21" s="17">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="H21" s="18">
-        <v>-13.868613138686</v>
+        <v>-16.793893129771</v>
       </c>
       <c r="I21" s="17">
-        <v>513</v>
+        <v>543</v>
       </c>
       <c r="J21" s="17">
-        <v>471</v>
+        <v>501</v>
       </c>
       <c r="K21" s="18">
-        <v>8.917197452229</v>
+        <v>8.383233532934</v>
       </c>
       <c r="L21" s="18">
-        <v>-2.656546489563</v>
+        <v>-4.063604240282</v>
       </c>
       <c r="M21" s="18">
-        <v>14.508928571428</v>
+        <v>15.042372881355</v>
       </c>
       <c r="N21" s="18">
-        <v>-61.515378844711</v>
+        <v>-61.652542372881</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>2</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>4</v>
       </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I22" s="14">
         <v>12</v>
       </c>
       <c r="J22" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K22" s="15">
-        <v>20</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L22" s="15">
-        <v>33.333333333333</v>
+        <v>20</v>
       </c>
       <c r="M22" s="15">
         <v>9.090909090909</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F23" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G23" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H23" s="15">
         <v>50</v>
       </c>
       <c r="I23" s="14">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J23" s="14">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K23" s="15">
-        <v>28.260869565217</v>
+        <v>25</v>
       </c>
       <c r="L23" s="15">
-        <v>18</v>
+        <v>7.142857142857</v>
       </c>
       <c r="M23" s="15">
-        <v>55.263157894736</v>
+        <v>53.846153846153</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D24" s="14">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E24" s="15">
-        <v>82.352941176470</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="F24" s="14">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G24" s="14">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="H24" s="15">
-        <v>-5.952380952380</v>
+        <v>-2.173913043478</v>
       </c>
       <c r="I24" s="14">
-        <v>383</v>
+        <v>407</v>
       </c>
       <c r="J24" s="14">
-        <v>333</v>
+        <v>360</v>
       </c>
       <c r="K24" s="15">
-        <v>15.015015015015</v>
+        <v>13.055555555555</v>
       </c>
       <c r="L24" s="15">
-        <v>17.846153846153</v>
+        <v>15.954415954416</v>
       </c>
       <c r="M24" s="15">
-        <v>8.192090395480</v>
+        <v>9.703504043126</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E25" s="15">
-        <v>33.333333333333</v>
+        <v>140</v>
       </c>
       <c r="F25" s="14">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G25" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H25" s="15">
-        <v>-35</v>
+        <v>4.347826086956</v>
       </c>
       <c r="I25" s="14">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="J25" s="14">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="K25" s="15">
-        <v>-1.980198019801</v>
+        <v>5.660377358490</v>
       </c>
       <c r="L25" s="15">
-        <v>-22.65625</v>
+        <v>-18.840579710144</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>35.714285714285</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G26" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H26" s="15">
-        <v>62.5</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I26" s="14">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="J26" s="14">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="K26" s="15">
-        <v>39.090909090909</v>
+        <v>37.931034482758</v>
       </c>
       <c r="L26" s="15">
-        <v>-16.847826086956</v>
+        <v>-17.948717948717</v>
       </c>
       <c r="M26" s="15">
-        <v>10.869565217391</v>
+        <v>8.108108108108</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,13 +1394,13 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
-      </c>
-      <c r="G27" s="14">
         <v>1</v>
       </c>
-      <c r="H27" s="15">
-        <v>100</v>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="14">
         <v>6</v>
@@ -1412,7 +1412,7 @@
         <v>50</v>
       </c>
       <c r="L27" s="15">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,31 +1426,31 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
         <v>2</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="14">
         <v>17</v>
       </c>
       <c r="J28" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K28" s="15">
-        <v>21.428571428571</v>
+        <v>6.25</v>
       </c>
       <c r="L28" s="15">
         <v>21.428571428571</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="14">
-        <v>2</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1493,8 +1493,8 @@
       <c r="K29" s="15">
         <v>150</v>
       </c>
-      <c r="L29" s="13" t="s">
-        <v>21</v>
+      <c r="L29" s="15">
+        <v>150</v>
       </c>
       <c r="M29" s="15">
         <v>0</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="14">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1534,8 +1534,8 @@
       <c r="K30" s="15">
         <v>50</v>
       </c>
-      <c r="L30" s="13" t="s">
-        <v>21</v>
+      <c r="L30" s="15">
+        <v>50</v>
       </c>
       <c r="M30" s="15">
         <v>-25</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>4</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1558,25 +1558,25 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G31" s="14">
         <v>8</v>
       </c>
       <c r="H31" s="15">
-        <v>-50</v>
+        <v>-37.5</v>
       </c>
       <c r="I31" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J31" s="14">
         <v>13</v>
       </c>
       <c r="K31" s="15">
-        <v>-46.153846153846</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="L31" s="15">
-        <v>-36.363636363636</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1616,26 +1616,26 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="14">
         <v>1</v>
       </c>
       <c r="H33" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" s="14">
         <v>1</v>
       </c>
       <c r="K33" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L33" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-090pct.xlsx
+++ b/data/source/weekly/cs-en-us-090pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -926,7 +926,7 @@
         <v>150</v>
       </c>
       <c r="N15" s="15">
-        <v>-61.538461538461</v>
+        <v>-64.285714285714</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
         <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G16" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H16" s="15">
-        <v>-35.714285714285</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J16" s="14">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K16" s="15">
-        <v>-19.672131147541</v>
+        <v>-20.3125</v>
       </c>
       <c r="L16" s="15">
-        <v>-9.259259259259</v>
+        <v>-16.393442622950</v>
       </c>
       <c r="M16" s="15">
-        <v>-51.485148514851</v>
+        <v>-53.636363636363</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.657430730478</v>
+        <v>-88</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>-60</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G17" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H17" s="15">
-        <v>-43.333333333333</v>
+        <v>-51.612903225806</v>
       </c>
       <c r="I17" s="14">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="J17" s="14">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="K17" s="15">
-        <v>2.150537634408</v>
+        <v>2.020202020202</v>
       </c>
       <c r="L17" s="15">
-        <v>2.150537634408</v>
+        <v>0</v>
       </c>
       <c r="M17" s="15">
-        <v>53.225806451612</v>
+        <v>53.030303030303</v>
       </c>
       <c r="N17" s="15">
-        <v>-43.452380952380</v>
+        <v>-45.108695652173</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E18" s="15">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G18" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H18" s="15">
-        <v>-57.894736842105</v>
+        <v>-50</v>
       </c>
       <c r="I18" s="14">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="J18" s="14">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K18" s="15">
-        <v>20.238095238095</v>
+        <v>18.681318681318</v>
       </c>
       <c r="L18" s="15">
-        <v>-20.472440944881</v>
+        <v>-20.588235294117</v>
       </c>
       <c r="M18" s="15">
-        <v>-11.403508771929</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="N18" s="15">
-        <v>-74.812967581047</v>
+        <v>-74.588235294117</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E19" s="15">
-        <v>53.846153846153</v>
+        <v>-68.181818181818</v>
       </c>
       <c r="F19" s="14">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G19" s="14">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="H19" s="15">
-        <v>3.636363636363</v>
+        <v>-19.354838709677</v>
       </c>
       <c r="I19" s="14">
+        <v>246</v>
+      </c>
+      <c r="J19" s="14">
         <v>240</v>
       </c>
-      <c r="J19" s="14">
-        <v>218</v>
-      </c>
       <c r="K19" s="15">
-        <v>10.091743119266</v>
+        <v>2.5</v>
       </c>
       <c r="L19" s="15">
-        <v>-1.639344262295</v>
+        <v>-1.992031872509</v>
       </c>
       <c r="M19" s="15">
-        <v>73.913043478260</v>
+        <v>69.655172413793</v>
       </c>
       <c r="N19" s="15">
-        <v>63.265306122449</v>
+        <v>55.696202531645</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>-20</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G20" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H20" s="15">
-        <v>30.769230769230</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="I20" s="14">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J20" s="14">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K20" s="15">
-        <v>33.333333333333</v>
+        <v>21.428571428571</v>
       </c>
       <c r="L20" s="15">
-        <v>36.842105263157</v>
+        <v>24.390243902439</v>
       </c>
       <c r="M20" s="15">
-        <v>-3.703703703703</v>
+        <v>-8.928571428571</v>
       </c>
       <c r="N20" s="15">
-        <v>-81.560283687943</v>
+        <v>-82.534246575342</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D21" s="17">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="E21" s="18">
-        <v>-6.666666666666</v>
+        <v>-46.341463414634</v>
       </c>
       <c r="F21" s="17">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="G21" s="17">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="H21" s="18">
-        <v>-16.793893129771</v>
+        <v>-30.555555555555</v>
       </c>
       <c r="I21" s="17">
-        <v>543</v>
+        <v>563</v>
       </c>
       <c r="J21" s="17">
-        <v>501</v>
+        <v>542</v>
       </c>
       <c r="K21" s="18">
-        <v>8.383233532934</v>
+        <v>3.874538745387</v>
       </c>
       <c r="L21" s="18">
-        <v>-4.063604240282</v>
+        <v>-6.166666666666</v>
       </c>
       <c r="M21" s="18">
-        <v>15.042372881355</v>
+        <v>11.264822134387</v>
       </c>
       <c r="N21" s="18">
-        <v>-61.652542372881</v>
+        <v>-62.616201859229</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="14">
+      <c r="C22" s="14">
         <v>1</v>
       </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G22" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="I22" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J22" s="14">
         <v>11</v>
       </c>
       <c r="K22" s="15">
-        <v>9.090909090909</v>
+        <v>18.181818181818</v>
       </c>
       <c r="L22" s="15">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M22" s="15">
-        <v>9.090909090909</v>
+        <v>18.181818181818</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1230,28 +1230,28 @@
         <v>-50</v>
       </c>
       <c r="F23" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G23" s="14">
         <v>8</v>
       </c>
       <c r="H23" s="15">
+        <v>12.5</v>
+      </c>
+      <c r="I23" s="14">
+        <v>61</v>
+      </c>
+      <c r="J23" s="14">
         <v>50</v>
       </c>
-      <c r="I23" s="14">
-        <v>60</v>
-      </c>
-      <c r="J23" s="14">
-        <v>48</v>
-      </c>
       <c r="K23" s="15">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L23" s="15">
-        <v>7.142857142857</v>
+        <v>-3.174603174603</v>
       </c>
       <c r="M23" s="15">
-        <v>53.846153846153</v>
+        <v>45.238095238095</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D24" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E24" s="15">
-        <v>-14.814814814814</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G24" s="14">
         <v>92</v>
       </c>
       <c r="H24" s="15">
-        <v>-2.173913043478</v>
+        <v>-3.260869565217</v>
       </c>
       <c r="I24" s="14">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="J24" s="14">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="K24" s="15">
-        <v>13.055555555555</v>
+        <v>7.948717948717</v>
       </c>
       <c r="L24" s="15">
-        <v>15.954415954416</v>
+        <v>12.868632707774</v>
       </c>
       <c r="M24" s="15">
-        <v>9.703504043126</v>
+        <v>3.950617283950</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D25" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15">
-        <v>140</v>
+        <v>-87.5</v>
       </c>
       <c r="F25" s="14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G25" s="14">
         <v>23</v>
       </c>
       <c r="H25" s="15">
-        <v>4.347826086956</v>
+        <v>0</v>
       </c>
       <c r="I25" s="14">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J25" s="14">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="K25" s="15">
-        <v>5.660377358490</v>
+        <v>-0.877192982456</v>
       </c>
       <c r="L25" s="15">
-        <v>-18.840579710144</v>
+        <v>-20.979020979021</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E26" s="15">
-        <v>33.333333333333</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="F26" s="14">
         <v>45</v>
       </c>
       <c r="G26" s="14">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H26" s="15">
-        <v>28.571428571428</v>
+        <v>15.384615384615</v>
       </c>
       <c r="I26" s="14">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="J26" s="14">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="K26" s="15">
-        <v>37.931034482758</v>
+        <v>30.534351145038</v>
       </c>
       <c r="L26" s="15">
-        <v>-17.948717948717</v>
+        <v>-16.585365853658</v>
       </c>
       <c r="M26" s="15">
-        <v>8.108108108108</v>
+        <v>6.875</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E28" s="15">
+        <v>-25</v>
+      </c>
+      <c r="F28" s="14">
+        <v>5</v>
+      </c>
+      <c r="G28" s="14">
+        <v>6</v>
+      </c>
+      <c r="H28" s="15">
+        <v>-16.666666666666</v>
+      </c>
+      <c r="I28" s="14">
+        <v>20</v>
+      </c>
+      <c r="J28" s="14">
+        <v>20</v>
+      </c>
+      <c r="K28" s="15">
         <v>0</v>
       </c>
-      <c r="F28" s="14">
-        <v>2</v>
-      </c>
-      <c r="G28" s="14">
-        <v>3</v>
-      </c>
-      <c r="H28" s="15">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="I28" s="14">
-        <v>17</v>
-      </c>
-      <c r="J28" s="14">
-        <v>16</v>
-      </c>
-      <c r="K28" s="15">
-        <v>6.25</v>
-      </c>
       <c r="L28" s="15">
-        <v>21.428571428571</v>
+        <v>25</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1494,13 +1494,13 @@
         <v>150</v>
       </c>
       <c r="L29" s="15">
-        <v>150</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M29" s="15">
         <v>0</v>
       </c>
       <c r="N29" s="15">
-        <v>-79.166666666666</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1535,13 +1535,13 @@
         <v>50</v>
       </c>
       <c r="L30" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M30" s="15">
         <v>-25</v>
       </c>
       <c r="N30" s="15">
-        <v>-86.956521739130</v>
+        <v>-89.655172413793</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1576,7 +1576,7 @@
         <v>-38.461538461538</v>
       </c>
       <c r="L31" s="15">
-        <v>-27.272727272727</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
